--- a/docs/KPI-Engine-Capabilities.xlsx
+++ b/docs/KPI-Engine-Capabilities.xlsx
@@ -9,17 +9,19 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework components" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision guide" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample dataset" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample monthly totals" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked examples" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Measure ops" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column functions" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Measure functions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hooks" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All operations" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YAML calculation patterns" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to extend" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Naming conventions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YAML preparation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision guide" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample dataset" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample monthly totals" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked examples" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Measure ops" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column functions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Measure functions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hooks" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All operations" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YAML calculation patterns" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to extend" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -228,108 +230,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="All_operations" displayName="All_operations" ref="A1:E29" headerRowCount="1">
-  <autoFilter ref="A1:E29"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Category"/>
-    <tableColumn id="2" name="Operation"/>
-    <tableColumn id="3" name="What it means"/>
-    <tableColumn id="4" name="YAML how-to"/>
-    <tableColumn id="5" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="YAML_calculation_patterns" displayName="YAML_calculation_patterns" ref="A1:E17" headerRowCount="1">
-  <autoFilter ref="A1:E17"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Pattern"/>
-    <tableColumn id="2" name="Intent"/>
-    <tableColumn id="3" name="YAML example"/>
-    <tableColumn id="4" name="Catalog names used"/>
-    <tableColumn id="5" name="Pitfall to avoid"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="How_to_extend" displayName="How_to_extend" ref="A1:E11" headerRowCount="1">
-  <autoFilter ref="A1:E11"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Goal"/>
-    <tableColumn id="2" name="Capability type"/>
-    <tableColumn id="3" name="Steps"/>
-    <tableColumn id="4" name="Files to change"/>
-    <tableColumn id="5" name="Do not"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Decision_guide" displayName="Decision_guide" ref="A1:E21" headerRowCount="1">
-  <autoFilter ref="A1:E21"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Step"/>
-    <tableColumn id="2" name="If you need…"/>
-    <tableColumn id="3" name="Use this"/>
-    <tableColumn id="4" name="Do not use"/>
-    <tableColumn id="5" name="Why / note"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Sample_dataset" displayName="Sample_dataset" ref="A1:H9" headerRowCount="1">
-  <autoFilter ref="A1:H9"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="event_month"/>
-    <tableColumn id="2" name="region"/>
-    <tableColumn id="3" name="order_id"/>
-    <tableColumn id="4" name="qty"/>
-    <tableColumn id="5" name="price"/>
-    <tableColumn id="6" name="shipped"/>
-    <tableColumn id="7" name="amount (qty×price)"/>
-    <tableColumn id="8" name="Note"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Sample_monthly_totals" displayName="Sample_monthly_totals" ref="A1:D13" headerRowCount="1">
-  <autoFilter ref="A1:D13"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="period"/>
-    <tableColumn id="2" name="grain"/>
-    <tableColumn id="3" name="revenue"/>
-    <tableColumn id="4" name="How it was added"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Worked_examples" displayName="Worked_examples" ref="A1:F11" headerRowCount="1">
-  <autoFilter ref="A1:F11"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="Example"/>
-    <tableColumn id="2" name="Components used"/>
-    <tableColumn id="3" name="Business question"/>
-    <tableColumn id="4" name="YAML"/>
-    <tableColumn id="5" name="Arithmetic on the sample (anchor Mar 2026)"/>
-    <tableColumn id="6" name="Takeaway"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Measure_ops" displayName="Measure_ops" ref="A1:K32" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Measure_functions" displayName="Measure_functions" ref="A1:K32" headerRowCount="1">
   <autoFilter ref="A1:K32"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Name"/>
@@ -348,9 +249,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Column_functions" displayName="Column_functions" ref="A1:K29" headerRowCount="1">
-  <autoFilter ref="A1:K29"/>
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Hooks" displayName="Hooks" ref="A1:K20" headerRowCount="1">
+  <autoFilter ref="A1:K20"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Role"/>
@@ -368,8 +269,137 @@
 </table>
 </file>
 
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="All_operations" displayName="All_operations" ref="A1:E29" headerRowCount="1">
+  <autoFilter ref="A1:E29"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Category"/>
+    <tableColumn id="2" name="Operation"/>
+    <tableColumn id="3" name="What it means"/>
+    <tableColumn id="4" name="YAML how-to"/>
+    <tableColumn id="5" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="YAML_calculation_patterns" displayName="YAML_calculation_patterns" ref="A1:E17" headerRowCount="1">
+  <autoFilter ref="A1:E17"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Pattern"/>
+    <tableColumn id="2" name="Intent"/>
+    <tableColumn id="3" name="YAML example"/>
+    <tableColumn id="4" name="Catalog names used"/>
+    <tableColumn id="5" name="Pitfall to avoid"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="How_to_extend" displayName="How_to_extend" ref="A1:E11" headerRowCount="1">
+  <autoFilter ref="A1:E11"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Goal"/>
+    <tableColumn id="2" name="Capability type"/>
+    <tableColumn id="3" name="Steps"/>
+    <tableColumn id="4" name="Files to change"/>
+    <tableColumn id="5" name="Do not"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Naming_conventions" displayName="Naming_conventions" ref="A1:E21" headerRowCount="1">
+  <autoFilter ref="A1:E21"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Topic"/>
+    <tableColumn id="2" name="Convention"/>
+    <tableColumn id="3" name="Do this"/>
+    <tableColumn id="4" name="Do not"/>
+    <tableColumn id="5" name="Engine rule"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="YAML_preparation" displayName="YAML_preparation" ref="A1:E22" headerRowCount="1">
+  <autoFilter ref="A1:E22"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Topic"/>
+    <tableColumn id="2" name="What to provide / emit"/>
+    <tableColumn id="3" name="Do this"/>
+    <tableColumn id="4" name="Do not"/>
+    <tableColumn id="5" name="Engine / AI rule"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Decision_guide" displayName="Decision_guide" ref="A1:E21" headerRowCount="1">
+  <autoFilter ref="A1:E21"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Step"/>
+    <tableColumn id="2" name="If you need…"/>
+    <tableColumn id="3" name="Use this"/>
+    <tableColumn id="4" name="Do not use"/>
+    <tableColumn id="5" name="Why / note"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Sample_dataset" displayName="Sample_dataset" ref="A1:H9" headerRowCount="1">
+  <autoFilter ref="A1:H9"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="event_month"/>
+    <tableColumn id="2" name="region"/>
+    <tableColumn id="3" name="order_id"/>
+    <tableColumn id="4" name="qty"/>
+    <tableColumn id="5" name="price"/>
+    <tableColumn id="6" name="shipped"/>
+    <tableColumn id="7" name="amount (qty×price)"/>
+    <tableColumn id="8" name="Note"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Sample_monthly_totals" displayName="Sample_monthly_totals" ref="A1:D13" headerRowCount="1">
+  <autoFilter ref="A1:D13"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="period"/>
+    <tableColumn id="2" name="grain"/>
+    <tableColumn id="3" name="revenue"/>
+    <tableColumn id="4" name="How it was added"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Worked_examples" displayName="Worked_examples" ref="A1:F11" headerRowCount="1">
+  <autoFilter ref="A1:F11"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Example"/>
+    <tableColumn id="2" name="Components used"/>
+    <tableColumn id="3" name="Business question"/>
+    <tableColumn id="4" name="YAML"/>
+    <tableColumn id="5" name="Arithmetic on the sample (anchor Mar 2026)"/>
+    <tableColumn id="6" name="Takeaway"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Measure_functions" displayName="Measure_functions" ref="A1:K32" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Measure_ops" displayName="Measure_ops" ref="A1:K32" headerRowCount="1">
   <autoFilter ref="A1:K32"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Name"/>
@@ -389,8 +419,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Hooks" displayName="Hooks" ref="A1:K20" headerRowCount="1">
-  <autoFilter ref="A1:K20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Column_functions" displayName="Column_functions" ref="A1:K29" headerRowCount="1">
+  <autoFilter ref="A1:K29"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Role"/>
@@ -697,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -770,83 +800,83 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Decision guide</t>
+          <t>Naming conventions</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>If you need X, use Y — stop at the first matching row</t>
+          <t>File names, kpi_id / model_id, identifiers, aliases, reserved words</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Walk top to bottom while authoring</t>
+          <t>Name every YAML file and key before writing formulas</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>If nothing matches: new catalog name, not core/</t>
+          <t>N/A — engine-enforced; do not invent a second spelling</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Sample dataset</t>
+          <t>YAML preparation</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Tiny order fact used by the worked examples (hand-checkable). Anchor = Mar 2026.</t>
+          <t>AI authoring contract: intake, calculation→YAML map, completeness checklist</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>N/A — teaching data, not production</t>
+          <t>Attach this sheet + catalogs + filled intake; AI must emit entire KPI YAML</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>kpi-yaml-preparation-guide.md §0 — do not invent ops; ask if intake is incomplete</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Sample monthly totals</t>
+          <t>Decision guide</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Oracle rollups of the sample (by month × region, 3m, worldwide)</t>
+          <t>If you need X, use Y — stop at the first matching row</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Use with Worked examples to check arithmetic</t>
+          <t>Walk top to bottom while authoring</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>If nothing matches: new catalog name, not core/</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Worked examples</t>
+          <t>Sample dataset</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Same dataset: YAML + arithmetic + expected JSON numbers</t>
+          <t>Tiny order fact used by the worked examples (hand-checkable). Anchor = Mar 2026.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Copy YAML into a KPI; numbers are the oracle for March 2026</t>
+          <t>N/A — teaching data, not production</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -858,173 +888,217 @@
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Measure ops</t>
+          <t>Sample monthly totals</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Every measures.op kind (point, window, rank, lag, …)</t>
+          <t>Oracle rollups of the sample (by month × region, 3m, worldwide)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>measures.&lt;key&gt;.op:</t>
+          <t>Use with Worked examples to check arithmetic</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>capabilities/ops/ + registries/ops.yaml</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Column functions</t>
+          <t>Worked examples</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Row-level functions on retrieved columns</t>
+          <t>Same dataset: YAML + arithmetic + expected JSON numbers</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>base_measures.*.columns + op:  or  expr: date_diff(…)</t>
+          <t>Copy YAML into a KPI; numbers are the oracle for March 2026</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>capabilities/functions/column/impl.py + registries/functions/column.yaml</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Measure functions</t>
+          <t>Measure ops</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Scalar functions on already-aggregated measures</t>
+          <t>Every measures.op kind (point, window, rank, lag, …)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>measures.*.op: fn  /  arithmetic  /  expr:</t>
+          <t>measures.&lt;key&gt;.op:</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>capabilities/functions/measure/impl.py + registries/functions/measure.yaml</t>
+          <t>capabilities/ops/ + registries/ops.yaml</t>
         </is>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Hooks</t>
+          <t>Column functions</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Series stats over the densified period spine</t>
+          <t>Row-level functions on retrieved columns</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>measures.*.op: hook  +  hook: &lt;name&gt;</t>
+          <t>base_measures.*.columns + op:  or  expr: date_diff(…)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>capabilities/hooks/impl.py + registries/hooks.yaml</t>
+          <t>capabilities/functions/column/impl.py + registries/functions/column.yaml</t>
         </is>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>All operations</t>
+          <t>Measure functions</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Aggs, OVER windows, HAVING, filters, time, cuts</t>
+          <t>Scalar functions on already-aggregated measures</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>base_measures / having / over / time / cuts</t>
+          <t>measures.*.op: fn  /  arithmetic  /  expr:</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Rare: contracts.py + core (new agg, filter op, time format)</t>
+          <t>capabilities/functions/measure/impl.py + registries/functions/measure.yaml</t>
         </is>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>YAML calculation patterns</t>
+          <t>Hooks</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>How to write typical KPI math (YoY, ratio, SLA, rank, …)</t>
+          <t>Series stats over the densified period spine</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Copy the pattern into config/kpis/&lt;id&gt;.yaml</t>
+          <t>measures.*.op: hook  +  hook: &lt;name&gt;</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>If no pattern fits, add a catalog name — do not edit core/</t>
+          <t>capabilities/hooks/impl.py + registries/hooks.yaml</t>
         </is>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>All operations</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Aggs, OVER windows, HAVING, filters, time, cuts</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>base_measures / having / over / time / cuts</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Rare: contracts.py + core (new agg, filter op, time format)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YAML calculation patterns</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>How to write typical KPI math (YoY, ratio, SLA, rank, …)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Copy the pattern into config/kpis/&lt;id&gt;.yaml</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>If no pattern fits, add a catalog name — do not edit core/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t>How to extend</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Step-by-step for each capability type</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>N/A — engine packaging</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Then regenerate registries/CAPABILITIES.md</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Start here: Framework components → Decision guide → Sample dataset → Worked examples.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Start here: Framework components → Naming conventions → YAML preparation → Decision guide → Sample dataset → Worked examples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Two calculation layers (do not mix them up)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="80" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>1) base_measures — per retrieved row, then fold with agg:. Identifiers are physical columns (and earlier helpers). Example: line_ratio: { expr: shipped / ordered, agg: sum } is the SUM of per-row ratios.
 2) measures — after aggregation, on the monthly/cut row. Identifiers are other measure keys. Example: fill_rate: { op: expr, expr: shipped_now / ordered_now } is SUM(shipped) / SUM(ordered).
@@ -1032,28 +1106,3092 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Host entry: udfs.kpi_engine.main   |   Routing: execution.kpi_id → config/kpis/&lt;id&gt;.yaml</t>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Host entry: udfs.kpi_engine.main   |   Routing: execution.kpi_id → config/kpis/&lt;id&gt;.yaml   |   AI brief: attach YAML preparation + catalogs + calculation intake (kpi-yaml-preparation-guide.md §0).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A20:D22"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Aliases</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>What it means</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>How to use in YAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>When to use / notes</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Python module</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Attr</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>min_args</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>requires_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="55" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Pass one retrieved column through unchanged.</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>amount:
+  columns: [amount]
+  op: value</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="55" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>abs</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Absolute value of one numeric column.</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>abs_delta:
+  columns: [delta]
+  op: abs</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>abs_columns</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="55" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Row-wise sum of two or more columns.</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>total:
+  columns: [a, b]
+  op: sum</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>sum_columns</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="55" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>subtract</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Row-wise left-to-right subtraction.</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>net:
+  columns: [gross, returns]
+  op: subtract</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>subtract_columns</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="55" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>multiply</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>mul, product</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Row-wise product of two or more columns.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>ontime_full:
+  columns: [ontime, fullqty]
+  op: multiply</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>multiply_columns</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="55" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>divide</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>div, ratio</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Row-wise numerator / denominator. Zero denominator is null.</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>rate:
+  columns: [shipped, ordered]
+  op: divide</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>divide_columns</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="55" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>percent_of</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Row-wise share of whole, scaled to 0-100.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>fill_pct:
+  columns: [filled, ordered]
+  op: percent_of</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>percent_of_columns</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="55" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Row-wise minimum of two or more columns.</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>lower:
+  columns: [a, b]
+  op: min</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>min_columns</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="55" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Row-wise maximum of two or more columns.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>upper:
+  columns: [a, b]
+  op: max</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>max_columns</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="55" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Row-wise mean of two or more columns.</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>mid:
+  columns: [a, b]
+  op: avg</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>avg_columns</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="55" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>coalesce</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>First non-null value on each row.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>picked:
+  columns: [preferred, fallback]
+  op: coalesce</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>coalesce_columns</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="55" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>if_null</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Value when present, otherwise the fallback column.</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>qty:
+  columns: { value: ordered_qty, fallback: planned_qty }
+  op: if_null</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>if_null_columns</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="55" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>nullif</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Null where value equals the sentinel column.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>nonzero:
+  columns: { value: amount, sentinel: offset_col }
+  op: nullif</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>nullif_columns</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="55" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>null_if_zero</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Null where the column is 0.</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>rate:
+  columns: [amount]
+  op: null_if_zero</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>null_if_zero_columns</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="55" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>zero_if_null</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>0 where the column is null.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>qty_or_zero:
+  columns: [ordered_qty]
+  op: zero_if_null</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>zero_if_null_columns</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="55" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>is_null</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>1 where the column is null, else 0.</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>missing:
+  columns: [amount]
+  op: is_null</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>is_null_columns</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="55" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>is_not_null</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>1 where the column is present, else 0.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>present:
+  columns: [amount]
+  op: is_not_null</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>is_not_null_columns</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="55" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>if_else</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Then-column where cond is nonzero, otherwise other.</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>picked:
+  columns: { cond: flag, then: amount, other: fallback }
+  op: if_else</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>if_else_columns</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="55" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>round</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Round a numeric column. Optional decimals defaults to 0.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>rounded:
+  columns: [amount]
+  op: round</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>round_columns</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="55" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>floor</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Floor of one numeric column.</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>whole:
+  columns: [amount]
+  op: floor</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>floor_columns</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="55" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>ceil</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Ceiling of one numeric column.</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>whole:
+  columns: [amount]
+  op: ceil</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>ceil_columns</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="55" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>base ** exp. Domain errors are null.</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>squared:
+  columns: { base: amount, exp: two }
+  op: power</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>power_columns</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="55" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>log</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Natural log. Non-positive is null.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>ln_amt:
+  columns: [amount]
+  op: log</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>log_columns</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="55" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>log10</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Base-10 log. Non-positive is null.</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>log_amt:
+  columns: [amount]
+  op: log10</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>log10_columns</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="55" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>sqrt</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Square root. Negative is null.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>root:
+  columns: [amount]
+  op: sqrt</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>sqrt_columns</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>date_diff</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>end minus start in day, week, month, or year. Null in either side is null.</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>gap:
+  expr: "date_diff(prev_date, order_date, 'day')"</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>date_diff_columns</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>date_add</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Add n day/week/month/year units to a date.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>next:
+  expr: "date_add(order_date, 1, 'month')"</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>date_add_columns</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="55" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>epoch_day</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Integer days since 1970-01-01.</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>epoch:
+  columns: [order_date]
+  op: epoch_day</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>epoch_day_columns</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Aliases</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>What it means</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>How to use in YAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>When to use / notes</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Python module</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Attr</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>min_args</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>requires_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="68" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>growth_pct</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>yoy, mom, percent_change</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Percent change between two scalars. Null or zero base yields null.</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>yoy:
+  op: fn
+  fn: growth_pct
+  inputs: [current_value, previous_year_value]</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>growth_pct</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="68" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>divide</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>div, ratio</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Ratio of two scalars. Zero or null denominator is null.</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>rate:
+  op: fn
+  fn: divide
+  inputs: [shipped, ordered]</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>divide_scalars</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="68" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>percent_of, share</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Share of whole, scaled to 0-100.</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>share:
+  op: fn
+  fn: percent
+  inputs: [part, whole]</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>percent_scalars</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="68" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Sum of two or more measure scalars. Any null yields null.</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>total:
+  op: fn
+  fn: sum
+  inputs: [a, b]</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>sum_scalars</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="68" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>subtract</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Left-to-right subtraction of measure scalars.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>net:
+  op: fn
+  fn: subtract
+  inputs: [gross, returns]</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>subtract_scalars</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="68" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>multiply</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>mul, product</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Product of two or more measure scalars.</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>weighted:
+  op: fn
+  fn: multiply
+  inputs: [qty, price]</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>multiply_scalars</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="68" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Minimum of the non-null measure scalars.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>lower:
+  op: fn
+  fn: min
+  inputs: [a, b]</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>min_scalars</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="68" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Maximum of the non-null measure scalars.</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>upper:
+  op: fn
+  fn: max
+  inputs: [a, b]</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>max_scalars</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="68" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Mean of the non-null measure scalars.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>mid:
+  op: fn
+  fn: avg
+  inputs: [a, b]</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>avg_scalars</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="68" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>abs</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Absolute value of one measure scalar.</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>magnitude:
+  op: fn
+  fn: abs
+  inputs: [gap]</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>abs_scalar</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="68" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>clamp</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Clamp a scalar into [lo, hi].</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>bounded:
+  op: fn
+  fn: clamp
+  inputs: [current_value, floor, cap]</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>clamp_scalars</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="68" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>attainment</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>actual / target × 100. Null or zero target is null.</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>vs_goal:
+  op: fn
+  fn: attainment
+  inputs: [current_value, target]</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>attainment</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="68" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>coalesce</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>First non-null measure scalar.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>picked:
+  op: fn
+  fn: coalesce
+  inputs: [current_value, target]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>coalesce_scalars</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="68" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>if_null</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Value when present, otherwise the fallback measure.</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>shown:
+  op: fn
+  fn: if_null
+  inputs: [current_value, target]</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>if_null_scalars</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="68" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>nullif</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Null when value equals the sentinel measure.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>nonzero:
+  op: fn
+  fn: nullif
+  inputs: [current_value, zero]</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>nullif_scalars</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="68" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>null_if_zero</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Null when the measure is 0.</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>rate:
+  op: fn
+  fn: null_if_zero
+  inputs: [current_value]</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>null_if_zero_scalars</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="68" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>zero_if_null</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>0 when the measure is null.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>shown:
+  op: fn
+  fn: zero_if_null
+  inputs: [current_value]</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>zero_if_null_scalars</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="68" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>is_null</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>1 if the measure is null, else 0.</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>missing:
+  op: fn
+  fn: is_null
+  inputs: [current_value]</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>is_null_scalars</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="68" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>is_not_null</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>1 if the measure is present, else 0.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>present:
+  op: fn
+  fn: is_not_null
+  inputs: [current_value]</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>is_not_null_scalars</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="68" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>if_else</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Then-measure if cond is nonzero, otherwise other.</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>picked:
+  op: fn
+  fn: if_else
+  inputs: { cond: flag, then: current_value, other: target }</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>if_else_scalars</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="68" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>sign_label</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>change_direction</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Positive / Negative / Neutral from a scalar. Null stays null; zero is Neutral.</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>direction:
+  op: fn
+  fn: sign_label
+  inputs: [yoy_month]</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>sign_label</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="68" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>round</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Round a measure scalar. Optional decimals defaults to 0.</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>rounded:
+  op: fn
+  fn: round
+  inputs: [current_value]</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>round_scalar</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="68" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>floor</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Floor of a measure scalar.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>whole:
+  op: fn
+  fn: floor
+  inputs: [current_value]</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>floor_scalar</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="68" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ceil</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Ceiling of a measure scalar.</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>whole:
+  op: fn
+  fn: ceil
+  inputs: [current_value]</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>ceil_scalar</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="68" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>base ** exp. Domain errors are null.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>squared:
+  op: fn
+  fn: power
+  inputs: [current_value, two]</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>power_scalars</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="68" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>log</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Natural log. Non-positive is null.</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>ln_amt:
+  op: fn
+  fn: log
+  inputs: [current_value]</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>log_scalar</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="68" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>log10</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Base-10 log. Non-positive is null.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>log_amt:
+  op: fn
+  fn: log10
+  inputs: [current_value]</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>log10_scalar</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="68" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>sqrt</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Square root. Negative is null.</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>root:
+  op: fn
+  fn: sqrt
+  inputs: [current_value]</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>sqrt_scalar</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="55" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>date_diff</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>end minus start in day, week, month, or year. Lists and trends are BindError.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>gap:
+  op: expr
+  expr: "date_diff(prev_date, ship_date, 'day')"</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>date_diff</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="81" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>date_add</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Add n day/week/month/year units to a date. Result is an ISO date string.</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>next:
+  op: fn
+  fn: date_add
+  inputs: [ship_date, one]
+  params: {unit: month}</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>date_add</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="68" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>epoch_day</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Integer days since 1970-01-01. Needs a date, not a number.</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>epoch:
+  op: fn
+  fn: epoch_day
+  inputs: [ship_date]</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>epoch_day</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2096,7 +5234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2871,7 +6009,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3453,7 +6591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4310,6 +7448,1219 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Convention</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Do this</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Do not</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Engine rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="29" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>KPI YAML file</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Path is exact: udfs/config/kpis/&lt;kpi_id&gt;.yaml. The stem must equal context.execution.kpi_id with no name-fold.</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>3004.yaml when execution.kpi_id is 3004 or "3004". Copy 3004.yaml to &lt;new_id&gt;.yaml.</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>sotif.yaml for kpi_id 3004. 3004.yml. kpis/Sotif.yaml when the host sends 3004. Spaces or extra folders.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>load_kpi opens only f"{kpi_id}.yaml". A missing file is a bind error. Case on the filename is OS-dependent; treat it as exact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="29" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>KPI yaml kpi_id:</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Set kpi_id: to the same value as the filename stem (and the host execution.kpi_id).</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>File 3004.yaml → kpi_id: 3004. File freight_fill.yaml → kpi_id: freight_fill.</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>File 3004.yaml with kpi_id: sotif. Reusing one YAML for several ids.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>The engine loads by filename. Inner kpi_id: is the spec id; keep it identical so logs and errors match the request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="29" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Model YAML file</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Path: udfs/config/models/&lt;model_id&gt;.yaml. Prefer lowercase snake_case. Extension must be .yaml.</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>sotif.yaml, orders_sql.yaml, freight_lane.yaml.</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>sotif.yml. models/Sotif Model.yaml. Putting the file under kpis/.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>load_model first tries &lt;model_id&gt;.yaml exactly. If missing, it accepts exactly one *.yaml whose stem folds to model_id (Sotif.yaml ↔ sotif). Two fold-matches is an error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="29" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Model yaml model_id:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>model_id: must equal the filename stem you intend KPIs to point at. Prefer the same spelling everywhere.</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>File sotif.yaml → model_id: sotif. File orders_sql.yaml → model_id: orders_sql.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>File sotif.yaml with model_id: sotif_sql. Two files that fold to the same id.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>KPI model: is matched to this field after folding case / spaces / underscores. Extra tokens do not fold away: sotif ≠ sotif_sql.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="29" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>KPI model: pointer</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>KPI YAML model: must name a model_id that exists. Same fold as model_id (case, spaces, underscores only).</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>model: sotif  with models/sotif.yaml. Per-base override base_measures.x.model: orders_sql when two extracts are needed.</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>model: sotif pointing at sotif_sql.yaml. Embedding an ADLS path instead of a model id. Inventing a model that has no file.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>same_model_id folds Region/region and my_model/my model. It does not treat sotif as sotif_sql. Physical vs sql is kind: on the model file, not a suffix rule — but keep suffixes honest (orders_sql.yaml for kind: sql).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="29" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Identifier alphabet</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>YAML names that become SQL/Pandas identifiers must match ^[A-Za-z_][A-Za-z0-9_]*$. Prefer snake_case.</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>reason_code, current_value, event_month, sotif_value, shipped_now.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>reason-code, reason.code, "Reason Code", 12m_trend, current value.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>require_ident rejects hyphens, dots, spaces, quotes, and leading digits. Used for dimensions, base_measures, parameters, aliases, sources, join keys, time.column, filter_map values, output_schema, columns: lists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="29" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Reserved words in formulas</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Do not use these as column or measure names inside expr: / CASE: case, when, then, else, and, or, not, is, null, in.</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>date_diff(start, end, 'day') — end is legal. Names like region, amount, shipped_now.</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>expr: case / qty. A column named when or in.</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Parser treats those as CASE/boolean keywords. end is a CASE terminator but is allowed as an identifier (date_diff(start, end, 'day')).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="29" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Name folding (host ↔ YAML)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Host keys fold onto YAML keys: lowercase, trim, spaces → underscore. Measure keys also try a compact fold (drop remaining underscores).</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>YAML current_value matches host Current_Value or current value. YAML previous_year_value matches PreviousYearValue.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Relying on fold for file names (KPI files do not fold). Expecting sotif to match sotif_sql. Two YAML keys that fold to the same spelling.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>norm_name is case/space/underscore only. Use one canonical snake_case in YAML; the host may send UI Title Case. Do not create two keys that collide after fold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="29" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Measure keys</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Keys under measures: are what context.measures_required[].measure_key must match (after fold). snake_case. Must not collide with parameters.</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>current_value, previous_year_value, trailing_3m, yoy_pct, fill_rate.</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Current Value as the YAML key. Reusing a parameter name. A key that is not in the host contract.</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Unknown measure_key is a bind error listing valid YAML keys. An empty measures_required list computes nothing (it does not expand to every key).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="29" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Base measure names</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Keys under base_measures: are internal facts. UI does not request these names. snake_case identifiers.</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>sotif_value, shipped_qty, ordered_qty, line_rev.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Naming a base the same as a requestable measure unless you intend identity. Hyphenated names.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Measures reference bases via of:. A base with no agg: is a row helper, not a requestable point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="29" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Dimensions</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Catalog names under dimensions[].name (and from: if the physical column differs). Request selected_dimensions must pick from this allowlist.</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>- { name: supplier, from: supplier_name }. default_dimensions: [reason_code].</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Inventing a request dimension not in YAML. Using the host display label as the YAML name when the column is supplier_name (map it with from:).</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>YAML owns the allowlist. from: is the physical/model column; name: is the grain token the request uses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="29" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Cut names</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Short stable tokens. G and R in 3004 are examples, not engine-hardcoded. default_cut must be one of the declared names.</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>cuts: [{ name: G, … }, { name: R, group_by: [region] }]. default_cut: G.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Renaming G/R in YAML without updating the host cut list. Two cuts with the same name.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Cut name is a string the host sends; group_by entries must be catalog dimensions (identifiers). Also_emit / ignore_filters name other cuts or filter codes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="29" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Dataset aliases</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>model.required_aliases and sources.*.alias must be identifiers. They bind to context.datasets by alias or key, case-insensitive.</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>required_aliases: [sotif]. Host dataset alias or key: sotif (or SOTIF).</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>required_aliases: [my-table]. Putting an ADLS URI in the alias. A KPI-level path instead of an alias.</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Context path wins; model default_path / default_paths fills gaps. Do not put dataset URIs in KPI YAML.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SQL model placeholders</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>kind: sql models reference bound datasets as $alias_path or $alias_scan (alias = required_aliases entry).</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>sql: |
+  SELECT … FROM $sotif_scan WHERE …</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Hard-coding /mnt/… or abfss:// in the SQL. Using an alias that is not in required_aliases.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>$alias_scan becomes delta_scan(?) or read_parquet(?) from table_type. $alias_path is the path parameter. Order of placeholders must match bind order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="29" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Time grains</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Only: day, week, month, quarter, year (lowercase). Default grain is month.</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>time: { column: event_month, grain: month, filter_code: reporting_month }.</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>time.grain: monthly. MTD as a grain name. execution.time_grain on the host payload.</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Send parameters.time_grain when the KPI declares that parameter. execution.time_grain is rejected. calendar: gregorian or fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="29" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>time.filter_code and filter_map keys</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>These are host filter codes, not SQL identifiers. They may contain spaces. filter_map values (columns) must still be identifiers.</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>filter_code: reporting_month. filter_map: { "Supplier Name": supplier_name }.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>filter_map values with spaces or hyphens. Omitting filter_code when time: is present.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>time.filter_code is required when time: is declared. It names the context filter that carries the selected period (the anchor), not a month IN list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="29" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Parameter names are identifiers. Must not equal a measure key. Do not declare selected_dimensions as a parameter. when: case labels cannot be param, cases, or else.</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>parameters: { time_grain: { type: string, allowed: [month, quarter] } }.</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>parameters.selected_dimensions. A case label named else. A parameter named current_value when that is also a measure key.</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>time_grain is the reserved overlay formerly on execution. Case labels param / cases / else are when: metadata keys.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="29" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Host UDF / module_path</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>One generic entry: udfs.kpi_engine.main. Routing is execution.kpi_id → config/kpis/&lt;id&gt;.yaml. Do not add a per-KPI Python module.</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Host module_path: udfs.kpi_engine.main. New KPI = new YAML (+ model YAML if the extract is new).</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>udfs/&lt;kpi_id&gt;/main.py. Cloning the engine per metric. A second module_path per kpi_id.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>The UDF is stateless compute(context). KPI math lives in YAML; DuckDB shape lives in model YAML.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="29" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>What must not live in KPI YAML</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>No dataset URIs, no Python, no invented op:/hook:/fn: names, no per-cut model:.</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>model: sotif. op: point / window / rank / hook / expr — names from this workbook's catalogs.</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>abfss://… in the KPI file. op: my_custom_yoy. cuts: [{ model: other }]. A sibling .py next to the YAML.</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Paths belong on context.datasets or model default_paths. Catalog names are the Measure ops / Functions / Hooks sheets. cuts cannot set model:.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="29" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>File header comments (recommended)</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Match existing config files: what the file provides, where it is used, capabilities, when to copy it.</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>See udfs/config/kpis/3004.yaml and udfs/config/models/sotif.yaml headers.</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Leaving a copied file with the old kpi_id / Sotif description. Putting secrets in comments.</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Comments are documentation only; the engine ignores them. Keep kpi_id / model_id in the body in sync with the filename.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>What to provide / emit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Do this</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Do not</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Engine / AI rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="29" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>How to brief an AI</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Attach this workbook (Naming conventions, this sheet, Measure ops, Column/Measure functions, Hooks, YAML patterns) plus kpi-yaml-preparation-guide.md §0 plus a filled intake.</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>One message: catalogs + intake + 'emit complete YAML, no TODOs'.</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>A one-line 'write YAML for fill rate' with no kpi_id, columns, or measure_keys.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>The AI may only use names on the catalog sheets. If intake is incomplete it must ask, not guess.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="29" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>AI output contract</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Every generating response is: (1) entire kpis/&lt;kpi_id&gt;.yaml (2) entire models/&lt;model_id&gt;.yaml if extract is new, else 'reuses existing model' (3) Assumptions (4) Gaps.</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Full files with header comments updated for this kpi_id. Then a short assumptions/gaps list.</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>A snippet, skeleton with blanks, # TODO, CHANGE_ME, or '...'. Partial measures: block.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>High confidence = completeness checklist all true. If any required key is unknown, ask numbered questions and emit no YAML.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="29" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Intake — identity</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>kpi_id (filename stem = execution.kpi_id exactly). model_id. reuse_existing_model yes/no. dataset_aliases.</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>kpi_id: 4120. model_id: sotif (reuse) or freight_lane (new). aliases: [sotif].</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Omitting kpi_id. Reusing sotif when the tables are different. Inventing a model_id that folds onto another file.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>See Naming conventions. .yaml only. Host module_path stays udfs.kpi_engine.main.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="29" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Intake — time or snapshot</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Either time.column + grain (day|week|month|quarter|year) + filter_code, or snapshot: true (omit time:).</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>time: { column: event_month, grain: month, filter_code: reporting_month, calendar: gregorian }.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Guessing reporting_month. execution.time_grain. Two values as a range. Defaulting to 'latest' when the filter is missing.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>The time filter is the anchor (exactly one value), never WHERE month IN (one month). Snapshot forbids window/trend/nonzero offset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="29" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Intake — grain and cuts</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>dimensions (name + from physical column). default_dimensions (required, [] = worldwide). At least one cut. default_cut.</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>dimensions: [{ name: region, from: region }]. cuts G extras-only group_by; exclude_from_grain / ignore_filters as needed.</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Inventing a host dimension not in YAML. Putting default_dimensions names again in cuts.group_by. Treating G/R as engine-hardcoded.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>YAML owns the allowlist. Request selected_dimensions only picks from it. Do not declare parameters.selected_dimensions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="29" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Intake — calculations</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Every host measure_key plus English/math. Physical columns DuckDB must retrieve. Optional filters: declarations.</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>measure_keys: [current_value, yoy_pct]. calculations.current_value: SUM(amount) at selected month.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>A calculation with no measure_key. A measure_key with no formula. Guessing column amount vs billed.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Unknown measure_key is a bind error. Empty measures_required computes nothing. Helpers the UI does not request go under base_measures only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Map — current period total</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>SUM/COUNT/MIN/MAX of a column at the selected period.</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>base_measures.fact: { sql: amount, agg: sum }
+measures.current_value: { of: fact, op: point, offset: { months: 0 } }</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>A measure op for the raw column. Free SQL SUM() in the KPI file.</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>agg: sum | avg | count | count_distinct | min | max | median | percentile | first | last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Map — previous period / YoY</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Same metric last year/month/quarter; growth % vs that period.</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>previous_year_value: { of: fact, op: point, offset: { years: 1 } }
+yoy_pct: { op: fn, fn: growth_pct, inputs: [current_value, previous_year_value] }</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>A window of length 1. Hand-coded (current-previous)/previous in SQL. fn: divide when the spec asked for %.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>growth_pct nulls when the base is null or zero. offset units: days weeks months quarters years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Map — trailing N / YTD / QTD</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Trailing N periods as one number; or named period-to-date.</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>value_3m: { of: fact, op: window, trailing: { months: 3 }, inclusive: true }
+value_qtd: { of: fact, op: window, range: qtd }</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Summing three point keys. range: qtd to mean trailing 3. wtd at month grain.</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>range: trailing | leading | cumulative | ytd | mtd | qtd | wtd | full_month | full_quarter | full_year. wtd needs day grain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="29" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Map — graph / trend</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Last N periods as an array for a chart.</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>trend_12m: { of: fact, op: trend, trailing: { months: 12 }, cuts: [G] }</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Returning N point keys. Unrestricted trend on a high-cardinality cut (50k cell cap).</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Trend defaults to default_cut if cuts: omitted. Axis lands in response trend_axes / trend_labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="29" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Map — ratio of totals vs sum of ratios</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Fill rate / rate KPIs: decide per-row then SUM vs SUM/SUM.</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Two summed bases → two points → measures.fill_rate: { op: expr, expr: shipped_now / ordered_now }</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>base expr shipped/ordered + agg: sum when the spec wanted ratio of totals.</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>base expr identifiers are physical columns. measure expr identifiers are other measure keys. Do not mix expr: with columns:/op:/sql: on one base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="29" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Map — share / rank / SLA</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Share of all groups on this cut; rank; hit-rate over a series.</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>op: percent_of_total (not fn: percent). op: rank. op: hook + hook: hit_rate + trailing: + value:.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>fn: percent for cut share. Sorting in the host to fake rank. A window SUM for 'how often'.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Cut ops see the full cut. Hooks need the densified spine — declare trailing so required_span is wide enough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="29" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Map — snapshot / entity window / lookup</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>No period column; per-entity sequence; static code map.</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Omit time:. over: on a pre-fold base (not calendar op: lag). lookup: { column, map, default }.</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>window/trend on a snapshot. Calendar op: lag for per-customer previous order. Giant CASE for a fee table.</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Snapshot leftover reporting_month skips as no_time. identity_grain required to point at a helper with no agg:.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="29" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Map — cannot express</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Iterative allocation, custom solver, anything with no catalog row.</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Stop. Report: cannot bind with current catalog. Name the missing op/fn/hook.</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Inventing op: my_yoy. eval() in YAML. A new udfs/&lt;kpi&gt;.py. Editing core/.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>New reusable names go in capabilities/ + registries/ (How to extend sheet). Do not fake them in this KPI file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="29" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory KPI keys</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>kpi_id, model, default_dimensions, ≥1 cut, ≥1 measure. time: (period) or omit entirely (snapshot). row_set span_union|anchor_only.</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>See gold file udfs/config/kpis/3004.yaml — copy structure, not Sotif names, unless this KPI is Sotif.</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Missing default_dimensions. Empty measures:. cuts[].model:. parameters.selected_dimensions.</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>cuts.group_by is extras only. Header comments must name this kpi_id, not leftover 3004 text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="29" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory model keys (new extract only)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>model_id, kind physical|sql, required_aliases, sources (physical) or sql:+output_schema (sql).</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>model_id matches filename and KPI model:. SQL uses $alias_scan / $alias_path, not hardcoded URIs.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>KPI-level sql: as the extract. A second model whose stem folds onto an existing file.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Context path wins over default_paths. Prefer $alias_scan so Delta vs Parquet follows table_type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="29" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Completeness checklist</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Emit YAML only when every box is true (same list as kpi-yaml-preparation-guide.md §0.7).</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Filename=kpi_id=execution.kpi_id; model matches; every host measure_key declared; every of:/expr ident exists; identifiers legal; time xor snapshot rules; no URIs; no invented names.</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Shipping 'best effort' YAML with guessed columns. Leaving one measure_key unimplemented.</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>If any box is false: numbered questions, no files. Closed-world names below (catalog sheets win if they disagree).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="29" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Closed-world — measure ops</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>measures.op may only be one of these names (live from registries/ops.yaml).</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>point, window, trend, arithmetic, fn, expr, constant, dimension, predicate, hook, rank, percent_of_total, ntile, dense_rank, row_number, cumulative_share, running_total, contribution, lag, lead, index, vs_target, threshold, percent_rank, gap_to_leader, gap_to_avg, zscore, running_avg, top_n, diff, pct_change</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Any other op: string, including aliases you invent.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>See Measure ops sheet for YAML shape. Aliases listed there (if any) are the only extra spellings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="29" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Closed-world — column functions</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>base_measures columns:+op: / expr call names (live from registries/functions/column.yaml).</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>value, abs, sum, subtract, multiply, divide, percent_of, min, max, avg, coalesce, if_null, nullif, null_if_zero, zero_if_null, is_null, is_not_null, if_else, round, floor, ceil, power, log, log10, sqrt, date_diff, date_add, epoch_day</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>SQL functions that are not on this list.</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>See Column functions sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="29" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Closed-world — measure functions</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>op: fn / arithmetic fn: names (live from registries/functions/measure.yaml).</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>growth_pct, divide, percent, sum, subtract, multiply, min, max, avg, abs, clamp, attainment, coalesce, if_null, nullif, null_if_zero, zero_if_null, is_null, is_not_null, if_else, sign_label, round, floor, ceil, power, log, log10, sqrt, date_diff, date_add, epoch_day</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>fn: yoy as a new name — use growth_pct (alias yoy/mom if listed on that sheet).</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>See Measure functions sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="29" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Closed-world — hooks</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>op: hook + hook: names (live from registries/hooks.yaml). Always declare trailing/offset so the scan is wide enough.</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>seasonal_index, ewma, period_max, period_min, period_median, period_avg, period_sum, hit_rate, streak, period_stdev, period_var, period_cv, period_range, period_count, miss_rate, miss_streak, longest_streak, cagr, slope</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>A hook name that is not listed. Using a window SUM as a substitute for hit_rate.</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>See Hooks sheet. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
@@ -4892,7 +9243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5233,7 +9584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5518,7 +9869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5940,3023 +10291,6 @@
           <t>attainment is a measure function. vs_target op can emit a gap instead of a percent.</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Aliases</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>What it means</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>How to use in YAML</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>When to use / notes</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Python module</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Attr</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>min_args</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>requires_value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="68" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>point</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr"/>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Value at the selected period, optional calendar offset.</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>previous_year_value:
-  op: point
-  of: sotif_value
-  offset: { years: 1 }</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.combo</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3" ht="68" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>window</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Trailing, leading, period-to-date, or full-period aggregate of a base measure.</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>value_qtd:
-  op: window
-  of: sotif_value
-  range: qtd</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.combo</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Window</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="68" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>trend</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Fixed-length period array plus a shared axis for graphs.</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>trend_12m:
-  op: trend
-  of: sotif_value
-  trailing: { months: 12 }</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.combo</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>Trend</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="68" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>arithmetic</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Combine other measures with a registered measure function (default divide).</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>ratio:
-  op: arithmetic
-  of: [current_value, previous_year_value]
-  fn: divide</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.combo</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Arithmetic</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="68" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>fn</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Feed other measures' scalars into a named measure function.</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>yoy:
-  op: fn
-  fn: growth_pct
-  inputs: [current_value, previous_year_value]</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.combo</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>Fn</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="55" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>expr</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Formula over other measures using + - * /.</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>blended:
-  op: expr
-  expr: (current_value + previous_year_value) / 2</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.combo</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Expr</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>constant</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>A literal number on every row.</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>target:
-  op: constant
-  value: 95</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.combo</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Constant</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>dimension</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Echo a grouping field as a requestable measure key.</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>region:
-  op: dimension</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.combo</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Dimension</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="94" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>predicate</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>1/0 flag when all (or any) measure predicates pass. Does not drop rows.</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>healthy:
-  op: predicate
-  match: all
-  predicates:
-    - { of: total_profit, cmp: gt, value: 0 }
-    - { of: return_rate, cmp: lt, value: 0.20 }</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.combo</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>Predicate</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="68" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>hook</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Call an allowlisted Python hook for logic the catalog cannot express.</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>custom:
-  op: hook
-  hook: seasonal_index
-  of: sotif_value</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.combo</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>Hook</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="68" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Rank groups on a cut. Ties share a rank; the next rank skips.</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>reason_rank:
-  op: rank
-  of: current_value
-  order: desc</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="68" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>percent_of_total</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Share of all groups on this cut (source * 100 / partition sum).</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>share:
-  op: percent_of_total
-  of: current_value
-  partition_by: [region]</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>PercentOfTotal</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14" ht="81" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>ntile</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Bucket groups into N tiles using RANK-style ties.</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>value_quartile:
-  op: ntile
-  of: current_value
-  tiles: 4
-  order: desc</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Ntile</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15" ht="68" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>dense_rank</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Rank groups on a cut. Ties share a rank; the next rank does not skip.</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>reason_dense_rank:
-  op: dense_rank
-  of: current_value
-  order: desc</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>DenseRank</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="68" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>row_number</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Unique 1..n order on a cut. Nulls sort last.</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>reason_row:
-  op: row_number
-  of: current_value
-  order: desc</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>RowNumber</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="68" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>cumulative_share</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Running share of of (Pareto). Last row in desc order is 100.</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>pareto:
-  op: cumulative_share
-  of: current_value
-  order: desc</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>CumulativeShare</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="68" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>running_total</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Ordered running sum of of on the cut.</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>running:
-  op: running_total
-  of: current_value
-  order: desc</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>RunningTotal</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="68" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>contribution</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Share of the cut's (of - vs) change. Who drove the movement.</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>yoy_contrib:
-  op: contribution
-  of: current_value
-  vs: previous_year_value</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Contribution</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20" ht="68" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>lag</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Value of a base, point, or window measure at offset before the anchor.</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>value_3m_ly:
-  op: lag
-  of: value_3m
-  offset: { years: 1 }</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.period</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>Lag</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr"/>
-      <c r="K20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="68" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Value of a base, point, or window measure at offset after the anchor.</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>next_month:
-  op: lead
-  of: current_value
-  offset: { months: 1 }</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.period</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22" ht="68" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>of / lagged of × 100. 100 means unchanged vs the offset period.</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>volume_index:
-  op: index
-  of: current_value
-  offset: { years: 1 }</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.period</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>vs_target</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Compare of to a target measure or literal (gap or percent).</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>gap:
-  op: vs_target
-  of: current_value
-  vs: target
-  as: gap</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.period</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>VsTarget</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>1 if of meets cmp vs a literal or measure, else 0.</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>hit_sla:
-  op: threshold
-  of: current_value
-  cmp: gte
-  value: 95</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.period</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>Threshold</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25" ht="68" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>percent_rank</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>RANK-style percent rank on a cut, scaled 0-100. One group is 0.</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>reason_pct_rank:
-  op: percent_rank
-  of: current_value
-  order: desc</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>PercentRank</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26" ht="55" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>gap_to_leader</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>of minus the partition max. The leader is 0.</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>vs_best:
-  op: gap_to_leader
-  of: current_value</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>GapToLeader</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27" ht="55" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>gap_to_avg</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>of minus the partition mean.</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>vs_typical:
-  op: gap_to_avg
-  of: current_value</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>GapToAvg</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28" ht="55" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>zscore</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>(of - mean) / sample stdev on the partition. Zero stdev is 0.</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>reason_z:
-  op: zscore
-  of: current_value</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>ZScore</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29" ht="68" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>running_avg</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Ordered running mean of of on the cut.</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>running_mean:
-  op: running_avg
-  of: current_value
-  order: desc</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>RunningAvg</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30" ht="81" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>top_n</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>1 if RANK() is &lt;= n, else 0. Ties can produce more than n ones.</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>top_reason:
-  op: top_n
-  of: current_value
-  n: 3
-  order: desc</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.cut</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>TopN</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31" ht="68" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>diff</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>of minus the same measure at offset before the anchor.</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>vs_last_year:
-  op: diff
-  of: current_value
-  offset: { years: 1 }</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.period</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32" ht="68" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>growth_pct(of, lagged of) at offset. Same scale as fn growth_pct.</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>yoy:
-  op: pct_change
-  of: current_value
-  offset: { years: 1 }</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.period</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>PctChange</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Aliases</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>What it means</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>How to use in YAML</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>When to use / notes</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Python module</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Attr</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>min_args</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>requires_value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="55" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Pass one retrieved column through unchanged.</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>amount:
-  columns: [amount]
-  op: value</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3" ht="55" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>abs</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Absolute value of one numeric column.</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>abs_delta:
-  columns: [delta]
-  op: abs</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>abs_columns</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="55" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>add</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Row-wise sum of two or more columns.</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>total:
-  columns: [a, b]
-  op: sum</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>sum_columns</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="55" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>subtract</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Row-wise left-to-right subtraction.</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>net:
-  columns: [gross, returns]
-  op: subtract</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>subtract_columns</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="55" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>multiply</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>mul, product</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Row-wise product of two or more columns.</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>ontime_full:
-  columns: [ontime, fullqty]
-  op: multiply</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>multiply_columns</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="55" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>divide</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>div, ratio</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Row-wise numerator / denominator. Zero denominator is null.</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>rate:
-  columns: [shipped, ordered]
-  op: divide</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>divide_columns</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>percent_of</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Row-wise share of whole, scaled to 0-100.</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>fill_pct:
-  columns: [filled, ordered]
-  op: percent_of</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>percent_of_columns</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="55" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Row-wise minimum of two or more columns.</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>lower:
-  columns: [a, b]
-  op: min</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>min_columns</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="55" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Row-wise maximum of two or more columns.</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>upper:
-  columns: [a, b]
-  op: max</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>max_columns</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="55" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>avg</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Row-wise mean of two or more columns.</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>mid:
-  columns: [a, b]
-  op: avg</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>avg_columns</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="55" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>coalesce</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>First non-null value on each row.</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>picked:
-  columns: [preferred, fallback]
-  op: coalesce</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>coalesce_columns</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="55" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>if_null</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Value when present, otherwise the fallback column.</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>qty:
-  columns: { value: ordered_qty, fallback: planned_qty }
-  op: if_null</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>if_null_columns</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14" ht="55" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>nullif</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Null where value equals the sentinel column.</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>nonzero:
-  columns: { value: amount, sentinel: offset_col }
-  op: nullif</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>nullif_columns</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15" ht="55" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>null_if_zero</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Null where the column is 0.</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>rate:
-  columns: [amount]
-  op: null_if_zero</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>null_if_zero_columns</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="55" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>zero_if_null</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>0 where the column is null.</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>qty_or_zero:
-  columns: [ordered_qty]
-  op: zero_if_null</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>zero_if_null_columns</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="55" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>is_null</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>1 where the column is null, else 0.</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>missing:
-  columns: [amount]
-  op: is_null</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>is_null_columns</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="55" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>is_not_null</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>1 where the column is present, else 0.</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>present:
-  columns: [amount]
-  op: is_not_null</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>is_not_null_columns</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="55" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>if_else</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Then-column where cond is nonzero, otherwise other.</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>picked:
-  columns: { cond: flag, then: amount, other: fallback }
-  op: if_else</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>if_else_columns</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20" ht="55" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>round</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Round a numeric column. Optional decimals defaults to 0.</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>rounded:
-  columns: [amount]
-  op: round</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>round_columns</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr"/>
-      <c r="K20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="55" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>floor</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Floor of one numeric column.</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>whole:
-  columns: [amount]
-  op: floor</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>floor_columns</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22" ht="55" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>ceil</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Ceiling of one numeric column.</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>whole:
-  columns: [amount]
-  op: ceil</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>ceil_columns</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="55" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>power</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>base ** exp. Domain errors are null.</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>squared:
-  columns: { base: amount, exp: two }
-  op: power</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>power_columns</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="55" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>log</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Natural log. Non-positive is null.</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>ln_amt:
-  columns: [amount]
-  op: log</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>log_columns</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25" ht="55" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>log10</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Base-10 log. Non-positive is null.</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>log_amt:
-  columns: [amount]
-  op: log10</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>log10_columns</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26" ht="55" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>sqrt</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Square root. Negative is null.</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>root:
-  columns: [amount]
-  op: sqrt</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>sqrt_columns</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>date_diff</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>end minus start in day, week, month, or year. Null in either side is null.</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>gap:
-  expr: "date_diff(prev_date, order_date, 'day')"</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>date_diff_columns</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>date_add</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Add n day/week/month/year units to a date.</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>next:
-  expr: "date_add(order_date, 1, 'month')"</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>date_add_columns</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29" ht="55" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>epoch_day</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Integer days since 1970-01-01.</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>epoch:
-  columns: [order_date]
-  op: epoch_day</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.column.impl</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>epoch_day_columns</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9048,7 +10382,7 @@
     <row r="2" ht="68" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>growth_pct</t>
+          <t>point</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -9061,17 +10395,205 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>yoy, mom, percent_change</t>
-        </is>
-      </c>
+      <c r="D2" s="5" t="inlineStr"/>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Percent change between two scalars. Null or zero base yields null.</t>
+          <t>Value at the selected period, optional calendar offset.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>previous_year_value:
+  op: point
+  of: sotif_value
+  offset: { years: 1 }</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="68" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Trailing, leading, period-to-date, or full-period aggregate of a base measure.</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>value_qtd:
+  op: window
+  of: sotif_value
+  range: qtd</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="68" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>trend</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Fixed-length period array plus a shared axis for graphs.</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>trend_12m:
+  op: trend
+  of: sotif_value
+  trailing: { months: 12 }</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="68" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Combine other measures with a registered measure function (default divide).</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>ratio:
+  op: arithmetic
+  of: [current_value, previous_year_value]
+  fn: divide</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="68" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Feed other measures' scalars into a named measure function.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>yoy:
   op: fn
@@ -9079,294 +10601,75 @@
   inputs: [current_value, previous_year_value]</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>growth_pct</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3" ht="68" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>divide</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Fn</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="55" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>expr</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>div, ratio</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Ratio of two scalars. Zero or null denominator is null.</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>rate:
-  op: fn
-  fn: divide
-  inputs: [shipped, ordered]</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>divide_scalars</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="68" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>percent_of, share</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Share of whole, scaled to 0-100.</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>share:
-  op: fn
-  fn: percent
-  inputs: [part, whole]</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>percent_scalars</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="68" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>add</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Sum of two or more measure scalars. Any null yields null.</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>total:
-  op: fn
-  fn: sum
-  inputs: [a, b]</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>sum_scalars</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="68" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>subtract</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Left-to-right subtraction of measure scalars.</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>net:
-  op: fn
-  fn: subtract
-  inputs: [gross, returns]</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>subtract_scalars</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="68" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>multiply</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>mul, product</t>
-        </is>
-      </c>
+      <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Product of two or more measure scalars.</t>
+          <t>Formula over other measures using + - * /.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>weighted:
-  op: fn
-  fn: multiply
-  inputs: [qty, price]</t>
+          <t>blended:
+  op: expr
+  expr: (current_value + previous_year_value) / 2</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.combo</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>multiply_scalars</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>Expr</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr"/>
     </row>
-    <row r="8" ht="68" customHeight="1">
+    <row r="8" ht="55" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>constant</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -9382,41 +10685,38 @@
       <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Minimum of the non-null measure scalars.</t>
+          <t>A literal number on every row.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>lower:
-  op: fn
-  fn: min
-  inputs: [a, b]</t>
+          <t>target:
+  op: constant
+  value: 95</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.combo</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>min_scalars</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>2</v>
-      </c>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr"/>
     </row>
-    <row r="9" ht="68" customHeight="1">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>dimension</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -9432,41 +10732,37 @@
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Maximum of the non-null measure scalars.</t>
+          <t>Echo a grouping field as a requestable measure key.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>upper:
-  op: fn
-  fn: max
-  inputs: [a, b]</t>
+          <t>region:
+  op: dimension</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.combo</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>max_scalars</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="68" customHeight="1">
+    <row r="10" ht="94" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>avg</t>
+          <t>predicate</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -9479,53 +10775,49 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Mean of the non-null measure scalars.</t>
+          <t>1/0 flag when all (or any) measure predicates pass. Does not drop rows.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>mid:
-  op: fn
-  fn: avg
-  inputs: [a, b]</t>
+          <t>healthy:
+  op: predicate
+  match: all
+  predicates:
+    - { of: total_profit, cmp: gt, value: 0 }
+    - { of: return_rate, cmp: lt, value: 0.20 }</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.combo</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>avg_scalars</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>2</v>
-      </c>
+          <t>Predicate</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="68" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>abs</t>
+          <t>hook</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>addon</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -9536,30 +10828,30 @@
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Absolute value of one measure scalar.</t>
+          <t>Call an allowlisted Python hook for logic the catalog cannot express.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>magnitude:
-  op: fn
-  fn: abs
-  inputs: [gap]</t>
+          <t>custom:
+  op: hook
+  hook: seasonal_index
+  of: sotif_value</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.combo</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>abs_scalar</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr"/>
@@ -9568,12 +10860,12 @@
     <row r="12" ht="68" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>clamp</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>addon</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -9584,30 +10876,30 @@
       <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Clamp a scalar into [lo, hi].</t>
+          <t>Rank groups on a cut. Ties share a rank; the next rank skips.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>bounded:
-  op: fn
-  fn: clamp
-  inputs: [current_value, floor, cap]</t>
+          <t>reason_rank:
+  op: rank
+  of: current_value
+  order: desc</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>clamp_scalars</t>
+          <t>Rank</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr"/>
@@ -9616,12 +10908,12 @@
     <row r="13" ht="68" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>attainment</t>
+          <t>percent_of_total</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>addon</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -9632,39 +10924,39 @@
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>actual / target × 100. Null or zero target is null.</t>
+          <t>Share of all groups on this cut (source * 100 / partition sum).</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>vs_goal:
-  op: fn
-  fn: attainment
-  inputs: [current_value, target]</t>
+          <t>share:
+  op: percent_of_total
+  of: current_value
+  partition_by: [region]</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>attainment</t>
+          <t>PercentOfTotal</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr"/>
     </row>
-    <row r="14" ht="68" customHeight="1">
+    <row r="14" ht="81" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>coalesce</t>
+          <t>ntile</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -9680,41 +10972,40 @@
       <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>First non-null measure scalar.</t>
+          <t>Bucket groups into N tiles using RANK-style ties.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>picked:
-  op: fn
-  fn: coalesce
-  inputs: [current_value, target]</t>
+          <t>value_quartile:
+  op: ntile
+  of: current_value
+  tiles: 4
+  order: desc</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>coalesce_scalars</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>2</v>
-      </c>
+          <t>Ntile</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="68" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>if_null</t>
+          <t>dense_rank</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -9730,30 +11021,30 @@
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Value when present, otherwise the fallback measure.</t>
+          <t>Rank groups on a cut. Ties share a rank; the next rank does not skip.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>shown:
-  op: fn
-  fn: if_null
-  inputs: [current_value, target]</t>
+          <t>reason_dense_rank:
+  op: dense_rank
+  of: current_value
+  order: desc</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>if_null_scalars</t>
+          <t>DenseRank</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr"/>
@@ -9762,7 +11053,7 @@
     <row r="16" ht="68" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>nullif</t>
+          <t>row_number</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -9778,30 +11069,30 @@
       <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Null when value equals the sentinel measure.</t>
+          <t>Unique 1..n order on a cut. Nulls sort last.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>nonzero:
-  op: fn
-  fn: nullif
-  inputs: [current_value, zero]</t>
+          <t>reason_row:
+  op: row_number
+  of: current_value
+  order: desc</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>nullif_scalars</t>
+          <t>RowNumber</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr"/>
@@ -9810,7 +11101,7 @@
     <row r="17" ht="68" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>null_if_zero</t>
+          <t>cumulative_share</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -9826,30 +11117,30 @@
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Null when the measure is 0.</t>
+          <t>Running share of of (Pareto). Last row in desc order is 100.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>rate:
-  op: fn
-  fn: null_if_zero
-  inputs: [current_value]</t>
+          <t>pareto:
+  op: cumulative_share
+  of: current_value
+  order: desc</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>null_if_zero_scalars</t>
+          <t>CumulativeShare</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
@@ -9858,7 +11149,7 @@
     <row r="18" ht="68" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>zero_if_null</t>
+          <t>running_total</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -9874,30 +11165,30 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>0 when the measure is null.</t>
+          <t>Ordered running sum of of on the cut.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>shown:
-  op: fn
-  fn: zero_if_null
-  inputs: [current_value]</t>
+          <t>running:
+  op: running_total
+  of: current_value
+  order: desc</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>zero_if_null_scalars</t>
+          <t>RunningTotal</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr"/>
@@ -9906,7 +11197,7 @@
     <row r="19" ht="68" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>is_null</t>
+          <t>contribution</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -9922,30 +11213,30 @@
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>1 if the measure is null, else 0.</t>
+          <t>Share of the cut's (of - vs) change. Who drove the movement.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>missing:
-  op: fn
-  fn: is_null
-  inputs: [current_value]</t>
+          <t>yoy_contrib:
+  op: contribution
+  of: current_value
+  vs: previous_year_value</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>is_null_scalars</t>
+          <t>Contribution</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr"/>
@@ -9954,7 +11245,7 @@
     <row r="20" ht="68" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>is_not_null</t>
+          <t>lag</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -9970,30 +11261,30 @@
       <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>1 if the measure is present, else 0.</t>
+          <t>Value of a base, point, or window measure at offset before the anchor.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>present:
-  op: fn
-  fn: is_not_null
-  inputs: [current_value]</t>
+          <t>value_3m_ly:
+  op: lag
+  of: value_3m
+  offset: { years: 1 }</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>is_not_null_scalars</t>
+          <t>Lag</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr"/>
@@ -10002,7 +11293,7 @@
     <row r="21" ht="68" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>if_else</t>
+          <t>lead</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -10018,30 +11309,30 @@
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Then-measure if cond is nonzero, otherwise other.</t>
+          <t>Value of a base, point, or window measure at offset after the anchor.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>picked:
-  op: fn
-  fn: if_else
-  inputs: { cond: flag, then: current_value, other: target }</t>
+          <t>next_month:
+  op: lead
+  of: current_value
+  offset: { months: 1 }</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>if_else_scalars</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
@@ -10050,12 +11341,12 @@
     <row r="22" ht="68" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>sign_label</t>
+          <t>index</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>addon</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -10063,51 +11354,47 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>change_direction</t>
-        </is>
-      </c>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Positive / Negative / Neutral from a scalar. Null stays null; zero is Neutral.</t>
+          <t>of / lagged of × 100. 100 means unchanged vs the offset period.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>direction:
-  op: fn
-  fn: sign_label
-  inputs: [yoy_month]</t>
+          <t>volume_index:
+  op: index
+  of: current_value
+  offset: { years: 1 }</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>sign_label</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr"/>
     </row>
-    <row r="23" ht="68" customHeight="1">
+    <row r="23" ht="81" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>round</t>
+          <t>vs_target</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>addon</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10118,44 +11405,45 @@
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Round a measure scalar. Optional decimals defaults to 0.</t>
+          <t>Compare of to a target measure or literal (gap or percent).</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>rounded:
-  op: fn
-  fn: round
-  inputs: [current_value]</t>
+          <t>gap:
+  op: vs_target
+  of: current_value
+  vs: target
+  as: gap</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>round_scalar</t>
+          <t>VsTarget</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr"/>
     </row>
-    <row r="24" ht="68" customHeight="1">
+    <row r="24" ht="81" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>floor</t>
+          <t>threshold</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>addon</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -10166,30 +11454,31 @@
       <c r="D24" s="5" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Floor of a measure scalar.</t>
+          <t>1 if of meets cmp vs a literal or measure, else 0.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>whole:
-  op: fn
-  fn: floor
-  inputs: [current_value]</t>
+          <t>hit_sla:
+  op: threshold
+  of: current_value
+  cmp: gte
+  value: 95</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>floor_scalar</t>
+          <t>Threshold</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr"/>
@@ -10198,12 +11487,12 @@
     <row r="25" ht="68" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>ceil</t>
+          <t>percent_rank</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>addon</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -10214,44 +11503,44 @@
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Ceiling of a measure scalar.</t>
+          <t>RANK-style percent rank on a cut, scaled 0-100. One group is 0.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>whole:
-  op: fn
-  fn: ceil
-  inputs: [current_value]</t>
+          <t>reason_pct_rank:
+  op: percent_rank
+  of: current_value
+  order: desc</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>ceil_scalar</t>
+          <t>PercentRank</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr"/>
     </row>
-    <row r="26" ht="68" customHeight="1">
+    <row r="26" ht="55" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>gap_to_leader</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>addon</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -10262,44 +11551,43 @@
       <c r="D26" s="5" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>base ** exp. Domain errors are null.</t>
+          <t>of minus the partition max. The leader is 0.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>squared:
-  op: fn
-  fn: power
-  inputs: [current_value, two]</t>
+          <t>vs_best:
+  op: gap_to_leader
+  of: current_value</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>power_scalars</t>
+          <t>GapToLeader</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr"/>
     </row>
-    <row r="27" ht="68" customHeight="1">
+    <row r="27" ht="55" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>log</t>
+          <t>gap_to_avg</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>addon</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -10310,44 +11598,43 @@
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Natural log. Non-positive is null.</t>
+          <t>of minus the partition mean.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>ln_amt:
-  op: fn
-  fn: log
-  inputs: [current_value]</t>
+          <t>vs_typical:
+  op: gap_to_avg
+  of: current_value</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>log_scalar</t>
+          <t>GapToAvg</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr"/>
     </row>
-    <row r="28" ht="68" customHeight="1">
+    <row r="28" ht="55" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>log10</t>
+          <t>zscore</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>addon</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -10358,30 +11645,29 @@
       <c r="D28" s="5" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Base-10 log. Non-positive is null.</t>
+          <t>(of - mean) / sample stdev on the partition. Zero stdev is 0.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>log_amt:
-  op: fn
-  fn: log10
-  inputs: [current_value]</t>
+          <t>reason_z:
+  op: zscore
+  of: current_value</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>log10_scalar</t>
+          <t>ZScore</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr"/>
@@ -10390,12 +11676,12 @@
     <row r="29" ht="68" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>sqrt</t>
+          <t>running_avg</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>addon</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -10406,44 +11692,44 @@
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Square root. Negative is null.</t>
+          <t>Ordered running mean of of on the cut.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>root:
-  op: fn
-  fn: sqrt
-  inputs: [current_value]</t>
+          <t>running_mean:
+  op: running_avg
+  of: current_value
+  order: desc</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>sqrt_scalar</t>
+          <t>RunningAvg</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr"/>
     </row>
-    <row r="30" ht="55" customHeight="1">
+    <row r="30" ht="81" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>date_diff</t>
+          <t>top_n</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>addon</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -10454,43 +11740,45 @@
       <c r="D30" s="5" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>end minus start in day, week, month, or year. Lists and trends are BindError.</t>
+          <t>1 if RANK() is &lt;= n, else 0. Ties can produce more than n ones.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>gap:
-  op: expr
-  expr: "date_diff(prev_date, ship_date, 'day')"</t>
+          <t>top_reason:
+  op: top_n
+  of: current_value
+  n: 3
+  order: desc</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>date_diff</t>
+          <t>TopN</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="5" t="inlineStr"/>
     </row>
-    <row r="31" ht="81" customHeight="1">
+    <row r="31" ht="68" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>date_add</t>
+          <t>diff</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>addon</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -10501,31 +11789,30 @@
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Add n day/week/month/year units to a date. Result is an ISO date string.</t>
+          <t>of minus the same measure at offset before the anchor.</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>next:
-  op: fn
-  fn: date_add
-  inputs: [ship_date, one]
-  params: {unit: month}</t>
+          <t>vs_last_year:
+  op: diff
+  of: current_value
+  offset: { years: 1 }</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>date_add</t>
+          <t>Diff</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr"/>
@@ -10534,12 +11821,12 @@
     <row r="32" ht="68" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>epoch_day</t>
+          <t>pct_change</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>addon</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -10550,30 +11837,30 @@
       <c r="D32" s="5" t="inlineStr"/>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Integer days since 1970-01-01. Needs a date, not a number.</t>
+          <t>growth_pct(of, lagged of) at offset. Same scale as fn growth_pct.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>epoch:
-  op: fn
-  fn: epoch_day
-  inputs: [ship_date]</t>
+          <t>yoy:
+  op: pct_change
+  of: current_value
+  offset: { years: 1 }</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine.capabilities.functions.measure.impl</t>
+          <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>epoch_day</t>
+          <t>PctChange</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr"/>

--- a/docs/KPI-Engine-Capabilities.xlsx
+++ b/docs/KPI-Engine-Capabilities.xlsx
@@ -312,8 +312,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Naming_conventions" displayName="Naming_conventions" ref="A1:E21" headerRowCount="1">
-  <autoFilter ref="A1:E21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Naming_conventions" displayName="Naming_conventions" ref="A1:E22" headerRowCount="1">
+  <autoFilter ref="A1:E22"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Topic"/>
     <tableColumn id="2" name="Convention"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Copy the pattern into config/kpis/&lt;id&gt;.yaml</t>
+          <t>Copy the pattern into config/kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1111,7 +1111,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Host entry: udfs.kpi_engine.main   |   Routing: execution.kpi_id → config/kpis/&lt;id&gt;.yaml   |   AI brief: attach YAML preparation + catalogs + calculation intake (kpi-yaml-preparation-guide.md §0).</t>
+          <t>Host entry: udfs.kpi_engine.main   |   Routing: execution.kpi_id → config/kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml   |   AI brief: attach YAML preparation + catalogs + calculation intake (kpi-yaml-preparation-guide.md §0).</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Copy config/kpis/3004.yaml → &lt;kpi_id&gt;.yaml. Fill time, dimensions, base_measures, cuts, measures. Host module_path stays udfs.kpi_engine.main.</t>
+          <t>Copy config/kpis/sotif/3004.yaml → &lt;kpi_group&gt;/&lt;kpi_id&gt;.yaml. Fill time, dimensions, base_measures, cuts, measures. Host module_path stays udfs.kpi_engine.main.</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>udfs/config/kpis/&lt;id&gt;.yaml</t>
+          <t>udfs/config/kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Add config/models/&lt;id&gt;.yaml (kind: physical or sql). Point KPI model: at model_id. Paths stay on context.datasets.</t>
+          <t>Add config/models/&lt;kpi_group&gt;/&lt;id&gt;.yaml (kind: physical or sql). Point KPI model: at model_id. Paths stay on context.datasets.</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>udfs/config/models/&lt;id&gt;.yaml</t>
+          <t>udfs/config/models/&lt;kpi_group&gt;/&lt;id&gt;.yaml</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>config/kpis/&lt;kpi_id&gt;.yaml</t>
+          <t>config/kpis/&lt;kpi_group&gt;/&lt;kpi_id&gt;.yaml (or flat kpis/&lt;kpi_id&gt;.yaml)</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>config/models/&lt;id&gt;.yaml  —  KPI model: pointer</t>
+          <t>config/models/&lt;kpi_group&gt;/&lt;id&gt;.yaml  —  KPI model: pointer</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -7445,7 +7445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7490,534 +7490,561 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Path is exact: udfs/config/kpis/&lt;kpi_id&gt;.yaml. The stem must equal context.execution.kpi_id with no name-fold.</t>
+          <t>Path: udfs/config/kpis/&lt;kpi_group&gt;/&lt;kpi_id&gt;.yaml or flat kpis/&lt;kpi_id&gt;.yaml. Stem equals execution.kpi_id exactly (no fold). kpi_id is unique across groups.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>3004.yaml when execution.kpi_id is 3004 or "3004". Copy 3004.yaml to &lt;new_id&gt;.yaml.</t>
+          <t>kpis/sotif/3004.yaml when execution.kpi_id is 3004. Copy to kpis/&lt;kpi_group&gt;/&lt;new_id&gt;.yaml.</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>sotif.yaml for kpi_id 3004. 3004.yml. kpis/Sotif.yaml when the host sends 3004. Spaces or extra folders.</t>
+          <t>sotif.yaml for kpi_id 3004. 3004.yml. Two groups both containing 3004.yaml. kpis/sotif/quality/3004.yaml (only one group folder).</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>load_kpi opens only f"{kpi_id}.yaml". A missing file is a bind error. Case on the filename is OS-dependent; treat it as exact.</t>
+          <t>load_kpi finds exactly one f"{kpi_id}.yaml" under kpis/ or kpis/*/. Zero or two files is a bind error. No execution.kpi_group field.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="29" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>KPI yaml kpi_id:</t>
+          <t>kpi_group folder</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Set kpi_id: to the same value as the filename stem (and the host execution.kpi_id).</t>
+          <t>One optional snake_case directory under kpis/ and models/. Authoring only; not sent on the context. Group names use the identifier alphabet.</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>File 3004.yaml → kpi_id: 3004. File freight_fill.yaml → kpi_id: freight_fill.</t>
+          <t>kpis/sotif/, models/sotif/, models/freight/. A KPI in kpis/sotif/ may model: a file in models/freight/.</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>File 3004.yaml with kpi_id: sotif. Reusing one YAML for several ids.</t>
+          <t>execution.kpi_group. Nested groups (kpis/a/b/id.yaml). Spaces or hyphens in the folder name.</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>The engine loads by filename. Inner kpi_id: is the spec id; keep it identical so logs and errors match the request.</t>
+          <t>The engine never reads the folder name. Duplicate kpi_id or model_id across groups is a bind error.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Model YAML file</t>
+          <t>KPI yaml kpi_id:</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Path: udfs/config/models/&lt;model_id&gt;.yaml. Prefer lowercase snake_case. Extension must be .yaml.</t>
+          <t>Set kpi_id: to the same value as the filename stem (and the host execution.kpi_id).</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>sotif.yaml, orders_sql.yaml, freight_lane.yaml.</t>
+          <t>File 3004.yaml → kpi_id: 3004. File freight_fill.yaml → kpi_id: freight_fill.</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>sotif.yml. models/Sotif Model.yaml. Putting the file under kpis/.</t>
+          <t>File 3004.yaml with kpi_id: sotif. Reusing one YAML for several ids.</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>load_model first tries &lt;model_id&gt;.yaml exactly. If missing, it accepts exactly one *.yaml whose stem folds to model_id (Sotif.yaml ↔ sotif). Two fold-matches is an error.</t>
+          <t>The engine loads by filename. Inner kpi_id: is the spec id; keep it identical so logs and errors match the request.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="29" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Model yaml model_id:</t>
+          <t>Model YAML file</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>model_id: must equal the filename stem you intend KPIs to point at. Prefer the same spelling everywhere.</t>
+          <t>Path: udfs/config/models/&lt;kpi_group&gt;/&lt;model_id&gt;.yaml or flat models/&lt;model_id&gt;.yaml. Prefer lowercase snake_case. Extension must be .yaml. model_id is unique across groups.</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>File sotif.yaml → model_id: sotif. File orders_sql.yaml → model_id: orders_sql.</t>
+          <t>models/sotif/sotif.yaml, models/freight/orders_sql.yaml.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>File sotif.yaml with model_id: sotif_sql. Two files that fold to the same id.</t>
+          <t>sotif.yml. models/Sotif Model.yaml. Two groups both containing sotif.yaml. Putting the file under kpis/.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>KPI model: is matched to this field after folding case / spaces / underscores. Extra tokens do not fold away: sotif ≠ sotif_sql.</t>
+          <t>load_model finds exactly one file whose stem folds to model_id among models/*.yaml and models/*/*.yaml (Sotif.yaml ↔ sotif). Two fold-matches is an error.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="29" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>KPI model: pointer</t>
+          <t>Model yaml model_id:</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>KPI YAML model: must name a model_id that exists. Same fold as model_id (case, spaces, underscores only).</t>
+          <t>model_id: must equal the filename stem you intend KPIs to point at. Prefer the same spelling everywhere.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>model: sotif  with models/sotif.yaml. Per-base override base_measures.x.model: orders_sql when two extracts are needed.</t>
+          <t>File sotif.yaml → model_id: sotif. File orders_sql.yaml → model_id: orders_sql.</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>model: sotif pointing at sotif_sql.yaml. Embedding an ADLS path instead of a model id. Inventing a model that has no file.</t>
+          <t>File sotif.yaml with model_id: sotif_sql. Two files that fold to the same id.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>same_model_id folds Region/region and my_model/my model. It does not treat sotif as sotif_sql. Physical vs sql is kind: on the model file, not a suffix rule — but keep suffixes honest (orders_sql.yaml for kind: sql).</t>
+          <t>KPI model: is matched to this field after folding case / spaces / underscores. Extra tokens do not fold away: sotif ≠ sotif_sql.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="29" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Identifier alphabet</t>
+          <t>KPI model: pointer</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>YAML names that become SQL/Pandas identifiers must match ^[A-Za-z_][A-Za-z0-9_]*$. Prefer snake_case.</t>
+          <t>KPI YAML model: must name a model_id that exists. Same fold as model_id (case, spaces, underscores only).</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>reason_code, current_value, event_month, sotif_value, shipped_now.</t>
+          <t>model: sotif  with models/sotif/sotif.yaml (or models/freight/sotif.yaml). Per-base override base_measures.x.model: orders_sql when two extracts are needed.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>reason-code, reason.code, "Reason Code", 12m_trend, current value.</t>
+          <t>model: sotif pointing at sotif_sql.yaml. Embedding an ADLS path instead of a model id. Inventing a model that has no file.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>require_ident rejects hyphens, dots, spaces, quotes, and leading digits. Used for dimensions, base_measures, parameters, aliases, sources, join keys, time.column, filter_map values, output_schema, columns: lists.</t>
+          <t>same_model_id folds Region/region and my_model/my model. It does not treat sotif as sotif_sql. Physical vs sql is kind: on the model file, not a suffix rule — but keep suffixes honest (orders_sql.yaml for kind: sql).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="29" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Reserved words in formulas</t>
+          <t>Identifier alphabet</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Do not use these as column or measure names inside expr: / CASE: case, when, then, else, and, or, not, is, null, in.</t>
+          <t>YAML names that become SQL/Pandas identifiers must match ^[A-Za-z_][A-Za-z0-9_]*$. Prefer snake_case.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>date_diff(start, end, 'day') — end is legal. Names like region, amount, shipped_now.</t>
+          <t>reason_code, current_value, event_month, sotif_value, shipped_now.</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>expr: case / qty. A column named when or in.</t>
+          <t>reason-code, reason.code, "Reason Code", 12m_trend, current value.</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Parser treats those as CASE/boolean keywords. end is a CASE terminator but is allowed as an identifier (date_diff(start, end, 'day')).</t>
+          <t>require_ident rejects hyphens, dots, spaces, quotes, and leading digits. Used for dimensions, base_measures, parameters, aliases, sources, join keys, time.column, filter_map values, output_schema, columns: lists.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="29" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Name folding (host ↔ YAML)</t>
+          <t>Reserved words in formulas</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Host keys fold onto YAML keys: lowercase, trim, spaces → underscore. Measure keys also try a compact fold (drop remaining underscores).</t>
+          <t>Do not use these as column or measure names inside expr: / CASE: case, when, then, else, and, or, not, is, null, in.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>YAML current_value matches host Current_Value or current value. YAML previous_year_value matches PreviousYearValue.</t>
+          <t>date_diff(start, end, 'day') — end is legal. Names like region, amount, shipped_now.</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Relying on fold for file names (KPI files do not fold). Expecting sotif to match sotif_sql. Two YAML keys that fold to the same spelling.</t>
+          <t>expr: case / qty. A column named when or in.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>norm_name is case/space/underscore only. Use one canonical snake_case in YAML; the host may send UI Title Case. Do not create two keys that collide after fold.</t>
+          <t>Parser treats those as CASE/boolean keywords. end is a CASE terminator but is allowed as an identifier (date_diff(start, end, 'day')).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="29" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Measure keys</t>
+          <t>Name folding (host ↔ YAML)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Keys under measures: are what context.measures_required[].measure_key must match (after fold). snake_case. Must not collide with parameters.</t>
+          <t>Host keys fold onto YAML keys: lowercase, trim, spaces → underscore. Measure keys also try a compact fold (drop remaining underscores).</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>current_value, previous_year_value, trailing_3m, yoy_pct, fill_rate.</t>
+          <t>YAML current_value matches host Current_Value or current value. YAML previous_year_value matches PreviousYearValue.</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Current Value as the YAML key. Reusing a parameter name. A key that is not in the host contract.</t>
+          <t>Relying on fold for file names (KPI files do not fold). Expecting sotif to match sotif_sql. Two YAML keys that fold to the same spelling.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Unknown measure_key is a bind error listing valid YAML keys. An empty measures_required list computes nothing (it does not expand to every key).</t>
+          <t>norm_name is case/space/underscore only. Use one canonical snake_case in YAML; the host may send UI Title Case. Do not create two keys that collide after fold.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="29" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Base measure names</t>
+          <t>Measure keys</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Keys under base_measures: are internal facts. UI does not request these names. snake_case identifiers.</t>
+          <t>Keys under measures: are what context.measures_required[].measure_key must match (after fold). snake_case. Must not collide with parameters.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>sotif_value, shipped_qty, ordered_qty, line_rev.</t>
+          <t>current_value, previous_year_value, trailing_3m, yoy_pct, fill_rate.</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Naming a base the same as a requestable measure unless you intend identity. Hyphenated names.</t>
+          <t>Current Value as the YAML key. Reusing a parameter name. A key that is not in the host contract.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Measures reference bases via of:. A base with no agg: is a row helper, not a requestable point.</t>
+          <t>Unknown measure_key is a bind error listing valid YAML keys. An empty measures_required list computes nothing (it does not expand to every key).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="29" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Dimensions</t>
+          <t>Base measure names</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Catalog names under dimensions[].name (and from: if the physical column differs). Request selected_dimensions must pick from this allowlist.</t>
+          <t>Keys under base_measures: are internal facts. UI does not request these names. snake_case identifiers.</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>- { name: supplier, from: supplier_name }. default_dimensions: [reason_code].</t>
+          <t>sotif_value, shipped_qty, ordered_qty, line_rev.</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Inventing a request dimension not in YAML. Using the host display label as the YAML name when the column is supplier_name (map it with from:).</t>
+          <t>Naming a base the same as a requestable measure unless you intend identity. Hyphenated names.</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>YAML owns the allowlist. from: is the physical/model column; name: is the grain token the request uses.</t>
+          <t>Measures reference bases via of:. A base with no agg: is a row helper, not a requestable point.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="29" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Cut names</t>
+          <t>Dimensions</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Short stable tokens. G and R in 3004 are examples, not engine-hardcoded. default_cut must be one of the declared names.</t>
+          <t>Catalog names under dimensions[].name (and from: if the physical column differs). Request selected_dimensions must pick from this allowlist.</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>cuts: [{ name: G, … }, { name: R, group_by: [region] }]. default_cut: G.</t>
+          <t>- { name: supplier, from: supplier_name }. default_dimensions: [reason_code].</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Renaming G/R in YAML without updating the host cut list. Two cuts with the same name.</t>
+          <t>Inventing a request dimension not in YAML. Using the host display label as the YAML name when the column is supplier_name (map it with from:).</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Cut name is a string the host sends; group_by entries must be catalog dimensions (identifiers). Also_emit / ignore_filters name other cuts or filter codes.</t>
+          <t>YAML owns the allowlist. from: is the physical/model column; name: is the grain token the request uses.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="29" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>Cut names</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Short stable tokens. G and R in 3004 are examples, not engine-hardcoded. default_cut must be one of the declared names.</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>cuts: [{ name: G, … }, { name: R, group_by: [region] }]. default_cut: G.</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Renaming G/R in YAML without updating the host cut list. Two cuts with the same name.</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Cut name is a string the host sends; group_by entries must be catalog dimensions (identifiers). Also_emit / ignore_filters name other cuts or filter codes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="29" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Dataset aliases</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>model.required_aliases and sources.*.alias must be identifiers. They bind to context.datasets by alias or key, case-insensitive.</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>required_aliases: [sotif]. Host dataset alias or key: sotif (or SOTIF).</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>required_aliases: [my-table]. Putting an ADLS URI in the alias. A KPI-level path instead of an alias.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Context path wins; model default_path / default_paths fills gaps. Do not put dataset URIs in KPI YAML.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>SQL model placeholders</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>kind: sql models reference bound datasets as $alias_path or $alias_scan (alias = required_aliases entry).</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>sql: |
   SELECT … FROM $sotif_scan WHERE …</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Hard-coding /mnt/… or abfss:// in the SQL. Using an alias that is not in required_aliases.</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>$alias_scan becomes delta_scan(?) or read_parquet(?) from table_type. $alias_path is the path parameter. Order of placeholders must match bind order.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="29" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Time grains</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Only: day, week, month, quarter, year (lowercase). Default grain is month.</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>time: { column: event_month, grain: month, filter_code: reporting_month }.</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>time.grain: monthly. MTD as a grain name. execution.time_grain on the host payload.</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Send parameters.time_grain when the KPI declares that parameter. execution.time_grain is rejected. calendar: gregorian or fiscal.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="29" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>time.filter_code and filter_map keys</t>
+          <t>Time grains</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>These are host filter codes, not SQL identifiers. They may contain spaces. filter_map values (columns) must still be identifiers.</t>
+          <t>Only: day, week, month, quarter, year (lowercase). Default grain is month.</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>filter_code: reporting_month. filter_map: { "Supplier Name": supplier_name }.</t>
+          <t>time: { column: event_month, grain: month, filter_code: reporting_month }.</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>filter_map values with spaces or hyphens. Omitting filter_code when time: is present.</t>
+          <t>time.grain: monthly. MTD as a grain name. execution.time_grain on the host payload.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>time.filter_code is required when time: is declared. It names the context filter that carries the selected period (the anchor), not a month IN list.</t>
+          <t>Send parameters.time_grain when the KPI declares that parameter. execution.time_grain is rejected. calendar: gregorian or fiscal.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="29" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>time.filter_code and filter_map keys</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Parameter names are identifiers. Must not equal a measure key. Do not declare selected_dimensions as a parameter. when: case labels cannot be param, cases, or else.</t>
+          <t>These are host filter codes, not SQL identifiers. They may contain spaces. filter_map values (columns) must still be identifiers.</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>parameters: { time_grain: { type: string, allowed: [month, quarter] } }.</t>
+          <t>filter_code: reporting_month. filter_map: { "Supplier Name": supplier_name }.</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>parameters.selected_dimensions. A case label named else. A parameter named current_value when that is also a measure key.</t>
+          <t>filter_map values with spaces or hyphens. Omitting filter_code when time: is present.</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>time_grain is the reserved overlay formerly on execution. Case labels param / cases / else are when: metadata keys.</t>
+          <t>time.filter_code is required when time: is declared. It names the context filter that carries the selected period (the anchor), not a month IN list.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="29" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Host UDF / module_path</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>One generic entry: udfs.kpi_engine.main. Routing is execution.kpi_id → config/kpis/&lt;id&gt;.yaml. Do not add a per-KPI Python module.</t>
+          <t>Parameter names are identifiers. Must not equal a measure key. Do not declare selected_dimensions as a parameter. when: case labels cannot be param, cases, or else.</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Host module_path: udfs.kpi_engine.main. New KPI = new YAML (+ model YAML if the extract is new).</t>
+          <t>parameters: { time_grain: { type: string, allowed: [month, quarter] } }.</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>udfs/&lt;kpi_id&gt;/main.py. Cloning the engine per metric. A second module_path per kpi_id.</t>
+          <t>parameters.selected_dimensions. A case label named else. A parameter named current_value when that is also a measure key.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>The UDF is stateless compute(context). KPI math lives in YAML; DuckDB shape lives in model YAML.</t>
+          <t>time_grain is the reserved overlay formerly on execution. Case labels param / cases / else are when: metadata keys.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="29" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>What must not live in KPI YAML</t>
+          <t>Host UDF / module_path</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>No dataset URIs, no Python, no invented op:/hook:/fn: names, no per-cut model:.</t>
+          <t>One generic entry: udfs.kpi_engine.main. Routing is execution.kpi_id → config/kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml (or flat kpis/&lt;id&gt;.yaml). Do not add a per-KPI Python module.</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>model: sotif. op: point / window / rank / hook / expr — names from this workbook's catalogs.</t>
+          <t>Host module_path: udfs.kpi_engine.main. New KPI = new YAML (+ model YAML if the extract is new).</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>abfss://… in the KPI file. op: my_custom_yoy. cuts: [{ model: other }]. A sibling .py next to the YAML.</t>
+          <t>udfs/&lt;kpi_id&gt;/main.py. Cloning the engine per metric. A second module_path per kpi_id.</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Paths belong on context.datasets or model default_paths. Catalog names are the Measure ops / Functions / Hooks sheets. cuts cannot set model:.</t>
+          <t>The UDF is stateless compute(context). KPI math lives in YAML; DuckDB shape lives in model YAML.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="29" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>What must not live in KPI YAML</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>No dataset URIs, no Python, no invented op:/hook:/fn: names, no per-cut model:.</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>model: sotif. op: point / window / rank / hook / expr — names from this workbook's catalogs.</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>abfss://… in the KPI file. op: my_custom_yoy. cuts: [{ model: other }]. A sibling .py next to the YAML.</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Paths belong on context.datasets or model default_paths. Catalog names are the Measure ops / Functions / Hooks sheets. cuts cannot set model:.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="29" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
           <t>File header comments (recommended)</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Match existing config files: what the file provides, where it is used, capabilities, when to copy it.</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>See udfs/config/kpis/3004.yaml and udfs/config/models/sotif.yaml headers.</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>See udfs/config/kpis/sotif/3004.yaml and udfs/config/models/sotif/sotif.yaml headers.</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Leaving a copied file with the old kpi_id / Sotif description. Putting secrets in comments.</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Comments are documentation only; the engine ignores them. Keep kpi_id / model_id in the body in sync with the filename.</t>
         </is>
@@ -8109,7 +8136,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Every generating response is: (1) entire kpis/&lt;kpi_id&gt;.yaml (2) entire models/&lt;model_id&gt;.yaml if extract is new, else 'reuses existing model' (3) Assumptions (4) Gaps.</t>
+          <t>Every generating response is: (1) entire kpis/&lt;kpi_group&gt;/&lt;kpi_id&gt;.yaml (2) entire models/&lt;kpi_group&gt;/&lt;model_id&gt;.yaml if extract is new, else 'reuses existing model' (3) Assumptions (4) Gaps.</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -8468,7 +8495,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>See gold file udfs/config/kpis/3004.yaml — copy structure, not Sotif names, unless this KPI is Sotif.</t>
+          <t>See gold file udfs/config/kpis/sotif/3004.yaml — copy structure, not Sotif names, unless this KPI is Sotif.</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">

--- a/docs/KPI-Engine-Capabilities.xlsx
+++ b/docs/KPI-Engine-Capabilities.xlsx
@@ -270,8 +270,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="All_operations" displayName="All_operations" ref="A1:E29" headerRowCount="1">
-  <autoFilter ref="A1:E29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="All_operations" displayName="All_operations" ref="A1:E30" headerRowCount="1">
+  <autoFilter ref="A1:E30"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Category"/>
     <tableColumn id="2" name="Operation"/>
@@ -326,8 +326,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="YAML_preparation" displayName="YAML_preparation" ref="A1:E22" headerRowCount="1">
-  <autoFilter ref="A1:E22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="YAML_preparation" displayName="YAML_preparation" ref="A1:E24" headerRowCount="1">
+  <autoFilter ref="A1:E24"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Topic"/>
     <tableColumn id="2" name="What to provide / emit"/>
@@ -5240,7 +5240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5361,25 +5361,29 @@
     <row r="5" ht="29" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Aggregation</t>
+          <t>Row helper</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>min / max</t>
+          <t>where:</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Recomputed at every cut (not summed regional extrema).</t>
+          <t>Pandas row mask before fold. Numeric ops coerce the compare column. ne excludes nulls (SQL-style).</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>base_measures.peak: { sql: amount, agg: max }</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
+          <t>where: { column: mrr, op: gt, value: 0 }</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Ops: in eq ne gt gte lt lte between. between needs values: [lo, hi]. Not like/is_null.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="29" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -5389,24 +5393,20 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>count_distinct</t>
+          <t>min / max</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Distinct values. Non-additive; re-reads row-level detail.</t>
+          <t>Recomputed at every cut (not summed regional extrema).</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>base_measures.n: { sql: order_id, agg: count_distinct }</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Not folded in DuckDB GROUP BY</t>
-        </is>
-      </c>
+          <t>base_measures.peak: { sql: amount, agg: max }</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="29" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -5416,22 +5416,22 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>median / percentile</t>
+          <t>count_distinct</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Non-additive. percentile requires percentile: 0–100.</t>
+          <t>Distinct values. Non-additive; re-reads row-level detail.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>base_measures.p90: { sql: amount, agg: percentile, percentile: 90 }</t>
+          <t>base_measures.n: { sql: order_id, agg: count_distinct }</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Row-level path</t>
+          <t>Not folded in DuckDB GROUP BY</t>
         </is>
       </c>
     </row>
@@ -5443,49 +5443,49 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>first / last</t>
+          <t>median / percentile</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Identity fold after sort by time (or window).</t>
+          <t>Non-additive. percentile requires percentile: 0–100.</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>base_measures.bal: { sql: balance, agg: last }</t>
+          <t>base_measures.p90: { sql: amount, agg: percentile, percentile: 90 }</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Used with over: last_n</t>
+          <t>Row-level path</t>
         </is>
       </c>
     </row>
     <row r="9" ht="29" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Row helper</t>
+          <t>Aggregation</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>expr</t>
+          <t>first / last</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Named row formula on columns or earlier helpers. No DuckDB SUM().</t>
+          <t>Identity fold after sort by time (or window). Text columns are still coerced to numeric.</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>gross: { expr: qty * price }</t>
+          <t>base_measures.bal: { sql: balance, agg: last }</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Add agg: to fold, or identity_grain for point of</t>
+          <t>Used with over: last_n</t>
         </is>
       </c>
     </row>
@@ -5497,20 +5497,24 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>lookup</t>
+          <t>expr</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Map a column through a dict; default or strict.</t>
+          <t>Named row formula on columns or earlier helpers. No DuckDB SUM().</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>fee: { lookup: { column: pay, map: { COD: 25 }, default: 10 } }</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr"/>
+          <t>gross: { expr: qty * price }</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Add agg: to fold, or identity_grain for point of</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="29" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -5520,17 +5524,17 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>sql: column</t>
+          <t>lookup</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Pass a physical column (or simple ident). Default agg is sum if omitted.</t>
+          <t>Map a column through a dict; default or strict.</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>sotif_value: { sql: amount, agg: sum }</t>
+          <t>fee: { lookup: { column: pay, map: { COD: 25 }, default: 10 } }</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -5543,49 +5547,45 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>columns + op</t>
+          <t>sql: column</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Call a column function by name.</t>
+          <t>Pass a physical column (or simple ident). Default agg is sum if omitted.</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>ontime_full: { columns: [ontime, fullqty], op: multiply, agg: sum }</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>See Column functions sheet</t>
-        </is>
-      </c>
+          <t>sotif_value: { sql: amount, agg: sum }</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="29" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Entity window</t>
+          <t>Row helper</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>over.lag / lead</t>
+          <t>columns + op</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Value from another row in partition, ordered by order_by. Requires of:.</t>
+          <t>Call a column function by name.</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>prev: { over: { fn: lag, of: order_date, partition_by: [customer_id], order_by: [order_date] }, agg: max }</t>
+          <t>ontime_full: { columns: [ontime, fullqty], op: multiply, agg: sum }</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Not calendar op: lag</t>
+          <t>See Column functions sheet</t>
         </is>
       </c>
     </row>
@@ -5597,20 +5597,24 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>over.row_number / rank / dense_rank</t>
+          <t>over.lag / lead</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Sequence in partition. of: optional.</t>
+          <t>Value from another row in partition, ordered by order_by. Requires of:.</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>seq: { over: { fn: row_number, partition_by: [customer_id], order_by: [order_date] }, agg: max }</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
+          <t>prev: { over: { fn: lag, of: order_date, partition_by: [customer_id], order_by: [order_date] }, agg: max }</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Not calendar op: lag</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="29" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -5620,17 +5624,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>over.running_sum / running_avg</t>
+          <t>over.row_number / rank / dense_rank</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Running aggregate along order_by. Requires of:.</t>
+          <t>Sequence in partition. of: optional.</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>run: { over: { fn: running_sum, of: net, partition_by: [carrier_id], order_by: [start] }, agg: max }</t>
+          <t>seq: { over: { fn: row_number, partition_by: [customer_id], order_by: [order_date] }, agg: max }</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -5643,49 +5647,45 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>over.last_n</t>
+          <t>over.running_sum / running_avg</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>JSON list of last n of values. Point only; cannot feed arithmetic.</t>
+          <t>Running aggregate along order_by. Requires of:.</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>recent: { over: { fn: last_n, of: amount, n: 2, partition_by: [region], order_by: [order_id] }, agg: last }</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Dates as ISO strings</t>
-        </is>
-      </c>
+          <t>run: { over: { fn: running_sum, of: net, partition_by: [carrier_id], order_by: [start] }, agg: max }</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="29" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Entity window</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>grain day/week/month/quarter/year</t>
+          <t>over.last_n</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Bucket of the time column. Fiscal calendar only for Q/Y.</t>
+          <t>JSON list of last n of values. Point only; cannot feed arithmetic.</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>time: { column: event_month, grain: month, filter_code: reporting_month }</t>
+          <t>recent: { over: { fn: last_n, of: amount, n: 2, partition_by: [region], order_by: [order_id] }, agg: last }</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>parameters.time_grain overlay if declared</t>
+          <t>Dates as ISO strings</t>
         </is>
       </c>
     </row>
@@ -5697,20 +5697,24 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>point offset</t>
+          <t>grain day/week/month/quarter/year</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Same measure at calendar offset from anchor.</t>
+          <t>Bucket of the time column. Fiscal calendar only for Q/Y.</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>previous_year_value: { of: sotif_value, op: point, offset: { years: 1 } }</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr"/>
+          <t>time: { column: event_month, grain: month, filter_code: reporting_month }</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>parameters.time_grain overlay if declared</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="29" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -5720,17 +5724,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>window trailing / leading</t>
+          <t>point offset</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Inclusive trailing N (or leading) periods as one number.</t>
+          <t>Same measure at calendar offset from anchor.</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>value_3m: { of: sotif_value, op: window, trailing: { months: 3 }, inclusive: true }</t>
+          <t>previous_year_value: { of: sotif_value, op: point, offset: { years: 1 } }</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -5743,24 +5747,20 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>window range</t>
+          <t>window trailing / leading</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>ytd, qtd, mtd, wtd, cumulative, full_month/quarter/year.</t>
+          <t>Inclusive trailing N (or leading) periods as one number.</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>value_qtd: { of: sotif_value, op: window, range: qtd }</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>wtd needs day grain</t>
-        </is>
-      </c>
+          <t>value_3m: { of: sotif_value, op: window, trailing: { months: 3 }, inclusive: true }</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="29" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -5770,22 +5770,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>trend</t>
+          <t>window range</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Fixed-length array + trend_axes / trend_labels. Cap 50,000 cells/cut.</t>
+          <t>ytd, qtd, mtd, wtd, cumulative, full_month/quarter/year.</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>trend_12m: { of: sotif_value, op: trend, trailing: { months: 12 } }</t>
+          <t>value_qtd: { of: sotif_value, op: window, range: qtd }</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Defaults to default_cut only</t>
+          <t>wtd needs day grain</t>
         </is>
       </c>
     </row>
@@ -5797,49 +5797,49 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>snapshot (omit time:)</t>
+          <t>trend</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>No month filter; all matching rows. Host reporting_month skipped as no_time.</t>
+          <t>Fixed-length array + trend_axes / trend_labels. Cap 50,000 cells/cut.</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Omit the time: block; only point offset 0 (and constants).</t>
+          <t>trend_12m: { of: sotif_value, op: trend, trailing: { months: 12 } }</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>No windows/trends/nonzero offsets</t>
+          <t>Defaults to default_cut only</t>
         </is>
       </c>
     </row>
     <row r="23" ht="29" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Cuts</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>group_by / ignore_filters / also_emit</t>
+          <t>snapshot (omit time:)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Named grains. G/R are examples, not hardcoded.</t>
+          <t>No month filter; all matching rows. Host reporting_month skipped as no_time.</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>cuts: [{ name: G, group_by: [], ignore_filters: [region], also_emit: [R] }]</t>
+          <t>Omit the time: block; only point offset 0 (and constants).</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>selected_dimensions overlays request grain</t>
+          <t>No windows/trends/nonzero offsets</t>
         </is>
       </c>
     </row>
@@ -5851,22 +5851,22 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>having</t>
+          <t>group_by / ignore_filters / also_emit</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Drop groups that fail measure predicates. Optional then_group_by.</t>
+          <t>Named grains. G/R are examples, not hardcoded.</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>having: { predicates: [{ of: current_value, cmp: gt, value: 0 }] }</t>
+          <t>cuts: [{ name: G, group_by: [], ignore_filters: [region], also_emit: [R] }]</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>cmp: gt gte lt lte eq ne between</t>
+          <t>selected_dimensions overlays request grain</t>
         </is>
       </c>
     </row>
@@ -5878,124 +5878,151 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>green_when</t>
+          <t>having</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Boolean green flag on survivors (above/below).</t>
+          <t>Drop groups that fail measure predicates. Optional then_group_by.</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>green_when: { of: current_value, above: 40 }</t>
+          <t>having: { predicates: [{ of: current_value, cmp: gt, value: 0 }] }</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Does not drop rows</t>
+          <t>cmp: gt gte lt lte eq ne between</t>
         </is>
       </c>
     </row>
     <row r="26" ht="29" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Cuts</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>apply extract / calc / result</t>
+          <t>green_when</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>DuckDB WHERE vs Pandas vs drop JSON rows.</t>
+          <t>Boolean green flag on survivors (above/below).</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>filters: { region: { apply: extract } }</t>
+          <t>green_when: { of: current_value, above: 40 }</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Unmapped valued filters are FilterError</t>
+          <t>Does not drop rows</t>
         </is>
       </c>
     </row>
     <row r="27" ht="29" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Multi-model</t>
+          <t>Filters</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>model_relations</t>
+          <t>apply extract / calc / result</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Join two extracts on declared keys.</t>
+          <t>DuckDB WHERE vs Pandas vs drop JSON rows.</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>model_relations: [{ left: a, right: b, on: [event_month, region], how: left }]</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr"/>
+          <t>filters: { region: { apply: extract } }</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Unmapped valued filters are FilterError</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="29" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Multi-model</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>identity_grain</t>
+          <t>model_relations</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Helpers as measures.of only when every emitted cut equals this grain.</t>
+          <t>Join two extracts on declared keys.</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>identity_grain: [carrier_id, shipment_id]</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Otherwise BindError; fold with agg:</t>
-        </is>
-      </c>
+          <t>model_relations: [{ left: a, right: b, on: [event_month, region], how: left }]</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
     </row>
     <row r="29" ht="29" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>identity_grain</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Helpers as measures.of only when every emitted cut equals this grain.</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>identity_grain: [carrier_id, shipment_id]</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Otherwise BindError; fold with agg:</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="29" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>SQL model</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>kind: sql</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Shape extract with CTEs; walked columns must be in output_schema.</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>models/&lt;id&gt;.yaml kind: sql + sql: + output_schema:</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Not KPI sql: formulas</t>
         </is>
@@ -8064,7 +8091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8322,350 +8349,406 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>Map — last period of a composite</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Lag/diff/index of a ratio, OEE, or rolling window — not a duplicated prior_* subgraph.</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>prior_oee: { op: lag, of: oee_pct, offset: { months: 1 } }
+delta: { op: diff, of: oee_pct, offset: { months: 1 } }</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>lag of trend/hook/rank. lag of a row helper (no agg:).</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Sources: bases and shiftable measures (point, window, fn, expr, …).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Map — row mask (where:)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>COUNT/SUM only the rows that pass a comparison (status, mrr &gt; 0, amount between).</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>where: { column: mrr, op: gt, value: 0 }
+between: { column: amount, op: between, values: [lo, hi] }</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>like / is_null on base where:. between with only value:.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Ops: in eq ne gt gte lt lte between. ne excludes nulls (SQL-style). Numeric ops coerce the column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>Map — trailing N / YTD / QTD</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Trailing N periods as one number; or named period-to-date.</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>value_3m: { of: fact, op: window, trailing: { months: 3 }, inclusive: true }
 value_qtd: { of: fact, op: window, range: qtd }</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Summing three point keys. range: qtd to mean trailing 3. wtd at month grain.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>range: trailing | leading | cumulative | ytd | mtd | qtd | wtd | full_month | full_quarter | full_year. wtd needs day grain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="29" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Map — graph / trend</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Last N periods as an array for a chart.</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>trend_12m: { of: fact, op: trend, trailing: { months: 12 }, cuts: [G] }</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Returning N point keys. Unrestricted trend on a high-cardinality cut (50k cell cap).</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Trend defaults to default_cut if cuts: omitted. Axis lands in response trend_axes / trend_labels.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="29" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Map — ratio of totals vs sum of ratios</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Fill rate / rate KPIs: decide per-row then SUM vs SUM/SUM.</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Two summed bases → two points → measures.fill_rate: { op: expr, expr: shipped_now / ordered_now }</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>base expr shipped/ordered + agg: sum when the spec wanted ratio of totals.</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>base expr identifiers are physical columns. measure expr identifiers are other measure keys. Do not mix expr: with columns:/op:/sql: on one base.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="29" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Map — share / rank / SLA</t>
+          <t>Map — graph / trend</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Share of all groups on this cut; rank; hit-rate over a series.</t>
+          <t>Last N periods as an array for a chart.</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>op: percent_of_total (not fn: percent). op: rank. op: hook + hook: hit_rate + trailing: + value:.</t>
+          <t>trend_12m: { of: fact, op: trend, trailing: { months: 12 }, cuts: [G] }</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>fn: percent for cut share. Sorting in the host to fake rank. A window SUM for 'how often'.</t>
+          <t>Returning N point keys. Unrestricted trend on a high-cardinality cut (50k cell cap).</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Cut ops see the full cut. Hooks need the densified spine — declare trailing so required_span is wide enough.</t>
+          <t>Trend defaults to default_cut if cuts: omitted. Axis lands in response trend_axes / trend_labels.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="29" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Map — snapshot / entity window / lookup</t>
+          <t>Map — ratio of totals vs sum of ratios</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>No period column; per-entity sequence; static code map.</t>
+          <t>Fill rate / rate KPIs: decide per-row then SUM vs SUM/SUM.</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Omit time:. over: on a pre-fold base (not calendar op: lag). lookup: { column, map, default }.</t>
+          <t>Two summed bases → two points → measures.fill_rate: { op: expr, expr: shipped_now / ordered_now }</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>window/trend on a snapshot. Calendar op: lag for per-customer previous order. Giant CASE for a fee table.</t>
+          <t>base expr shipped/ordered + agg: sum when the spec wanted ratio of totals.</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Snapshot leftover reporting_month skips as no_time. identity_grain required to point at a helper with no agg:.</t>
+          <t>base expr identifiers are physical columns. measure expr identifiers are other measure keys. Do not mix expr: with columns:/op:/sql: on one base.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="29" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Map — cannot express</t>
+          <t>Map — share / rank / SLA</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Iterative allocation, custom solver, anything with no catalog row.</t>
+          <t>Share of all groups on this cut; rank; hit-rate over a series.</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Stop. Report: cannot bind with current catalog. Name the missing op/fn/hook.</t>
+          <t>op: percent_of_total (not fn: percent). op: rank. op: hook + hook: hit_rate + trailing: + value:.</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Inventing op: my_yoy. eval() in YAML. A new udfs/&lt;kpi&gt;.py. Editing core/.</t>
+          <t>fn: percent for cut share. Sorting in the host to fake rank. A window SUM for 'how often'.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>New reusable names go in capabilities/ + registries/ (How to extend sheet). Do not fake them in this KPI file.</t>
+          <t>Cut ops see the full cut. Hooks need the densified spine — declare trailing so required_span is wide enough.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="29" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Mandatory KPI keys</t>
+          <t>Map — snapshot / entity window / lookup</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>kpi_id, model, default_dimensions, ≥1 cut, ≥1 measure. time: (period) or omit entirely (snapshot). row_set span_union|anchor_only.</t>
+          <t>No period column; per-entity sequence; static code map.</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>See gold file udfs/config/kpis/sotif/3004.yaml — copy structure, not Sotif names, unless this KPI is Sotif.</t>
+          <t>Omit time:. over: on a pre-fold base (not calendar op: lag). lookup: { column, map, default }.</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Missing default_dimensions. Empty measures:. cuts[].model:. parameters.selected_dimensions.</t>
+          <t>window/trend on a snapshot. Calendar op: lag for per-customer previous order. Giant CASE for a fee table.</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>cuts.group_by is extras only. Header comments must name this kpi_id, not leftover 3004 text.</t>
+          <t>Snapshot leftover reporting_month skips as no_time. identity_grain required to point at a helper with no agg:.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="29" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Mandatory model keys (new extract only)</t>
+          <t>Map — cannot express</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>model_id, kind physical|sql, required_aliases, sources (physical) or sql:+output_schema (sql).</t>
+          <t>Iterative allocation, custom solver, anything with no catalog row.</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>model_id matches filename and KPI model:. SQL uses $alias_scan / $alias_path, not hardcoded URIs.</t>
+          <t>Stop. Report: cannot bind with current catalog. Name the missing op/fn/hook.</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>KPI-level sql: as the extract. A second model whose stem folds onto an existing file.</t>
+          <t>Inventing op: my_yoy. eval() in YAML. A new udfs/&lt;kpi&gt;.py. Editing core/.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Context path wins over default_paths. Prefer $alias_scan so Delta vs Parquet follows table_type.</t>
+          <t>New reusable names go in capabilities/ + registries/ (How to extend sheet). Do not fake them in this KPI file.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="29" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Completeness checklist</t>
+          <t>Mandatory KPI keys</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Emit YAML only when every box is true (same list as kpi-yaml-preparation-guide.md §0.7).</t>
+          <t>kpi_id, model, default_dimensions, ≥1 cut, ≥1 measure. time: (period) or omit entirely (snapshot). row_set span_union|anchor_only.</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Filename=kpi_id=execution.kpi_id; model matches; every host measure_key declared; every of:/expr ident exists; identifiers legal; time xor snapshot rules; no URIs; no invented names.</t>
+          <t>See gold file udfs/config/kpis/sotif/3004.yaml — copy structure, not Sotif names, unless this KPI is Sotif.</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Shipping 'best effort' YAML with guessed columns. Leaving one measure_key unimplemented.</t>
+          <t>Missing default_dimensions. Empty measures:. cuts[].model:. parameters.selected_dimensions.</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>If any box is false: numbered questions, no files. Closed-world names below (catalog sheets win if they disagree).</t>
+          <t>cuts.group_by is extras only. Header comments must name this kpi_id, not leftover 3004 text.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="29" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Closed-world — measure ops</t>
+          <t>Mandatory model keys (new extract only)</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>measures.op may only be one of these names (live from registries/ops.yaml).</t>
+          <t>model_id, kind physical|sql, required_aliases, sources (physical) or sql:+output_schema (sql).</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>point, window, trend, arithmetic, fn, expr, constant, dimension, predicate, hook, rank, percent_of_total, ntile, dense_rank, row_number, cumulative_share, running_total, contribution, lag, lead, index, vs_target, threshold, percent_rank, gap_to_leader, gap_to_avg, zscore, running_avg, top_n, diff, pct_change</t>
+          <t>model_id matches filename and KPI model:. SQL uses $alias_scan / $alias_path, not hardcoded URIs.</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Any other op: string, including aliases you invent.</t>
+          <t>KPI-level sql: as the extract. A second model whose stem folds onto an existing file.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>See Measure ops sheet for YAML shape. Aliases listed there (if any) are the only extra spellings.</t>
+          <t>Context path wins over default_paths. Prefer $alias_scan so Delta vs Parquet follows table_type.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="29" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Closed-world — column functions</t>
+          <t>Completeness checklist</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>base_measures columns:+op: / expr call names (live from registries/functions/column.yaml).</t>
+          <t>Emit YAML only when every box is true (same list as kpi-yaml-preparation-guide.md §0.7).</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>value, abs, sum, subtract, multiply, divide, percent_of, min, max, avg, coalesce, if_null, nullif, null_if_zero, zero_if_null, is_null, is_not_null, if_else, round, floor, ceil, power, log, log10, sqrt, date_diff, date_add, epoch_day</t>
+          <t>Filename=kpi_id=execution.kpi_id; model matches; every host measure_key declared; every of:/expr ident exists; identifiers legal; time xor snapshot rules; no URIs; no invented names.</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>SQL functions that are not on this list.</t>
+          <t>Shipping 'best effort' YAML with guessed columns. Leaving one measure_key unimplemented.</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>See Column functions sheet.</t>
+          <t>If any box is false: numbered questions, no files. Closed-world names below (catalog sheets win if they disagree).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="29" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Closed-world — measure functions</t>
+          <t>Closed-world — measure ops</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>op: fn / arithmetic fn: names (live from registries/functions/measure.yaml).</t>
+          <t>measures.op may only be one of these names (live from registries/ops.yaml).</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>growth_pct, divide, percent, sum, subtract, multiply, min, max, avg, abs, clamp, attainment, coalesce, if_null, nullif, null_if_zero, zero_if_null, is_null, is_not_null, if_else, sign_label, round, floor, ceil, power, log, log10, sqrt, date_diff, date_add, epoch_day</t>
+          <t>point, window, trend, arithmetic, fn, expr, constant, dimension, predicate, hook, rank, percent_of_total, ntile, dense_rank, row_number, cumulative_share, running_total, contribution, lag, lead, index, vs_target, threshold, percent_rank, gap_to_leader, gap_to_avg, zscore, running_avg, top_n, diff, pct_change</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>fn: yoy as a new name — use growth_pct (alias yoy/mom if listed on that sheet).</t>
+          <t>Any other op: string, including aliases you invent.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>See Measure functions sheet.</t>
+          <t>See Measure ops sheet for YAML shape. Aliases listed there (if any) are the only extra spellings.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="29" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>Closed-world — column functions</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>base_measures columns:+op: / expr call names (live from registries/functions/column.yaml).</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>value, abs, sum, subtract, multiply, divide, percent_of, min, max, avg, coalesce, if_null, nullif, null_if_zero, zero_if_null, is_null, is_not_null, if_else, round, floor, ceil, power, log, log10, sqrt, date_diff, date_add, epoch_day</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>SQL functions that are not on this list.</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>See Column functions sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="29" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Closed-world — measure functions</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>op: fn / arithmetic fn: names (live from registries/functions/measure.yaml).</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>growth_pct, divide, percent, sum, subtract, multiply, min, max, avg, abs, clamp, attainment, coalesce, if_null, nullif, null_if_zero, zero_if_null, is_null, is_not_null, if_else, sign_label, round, floor, ceil, power, log, log10, sqrt, date_diff, date_add, epoch_day</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>fn: yoy as a new name — use growth_pct (alias yoy/mom if listed on that sheet).</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>See Measure functions sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="29" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
           <t>Closed-world — hooks</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>op: hook + hook: names (live from registries/hooks.yaml). Always declare trailing/offset so the scan is wide enough.</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>seasonal_index, ewma, period_max, period_min, period_median, period_avg, period_sum, hit_rate, streak, period_stdev, period_var, period_cv, period_range, period_count, miss_rate, miss_streak, longest_streak, cagr, slope</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>A hook name that is not listed. Using a window SUM as a substitute for hit_rate.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>See Hooks sheet. Hooks that list requires_value need value:.</t>
         </is>
@@ -11288,7 +11371,7 @@
       <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Value of a base, point, or window measure at offset before the anchor.</t>
+          <t>Value of a base or shiftable measure at offset before the anchor.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -11336,7 +11419,7 @@
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Value of a base, point, or window measure at offset after the anchor.</t>
+          <t>Value of a base or shiftable measure at offset after the anchor.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -11384,7 +11467,7 @@
       <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>of / lagged of × 100. 100 means unchanged vs the offset period.</t>
+          <t>of / lagged of × 100. Source is a base or shiftable measure. 100 means unchanged vs the offset period.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -11816,7 +11899,7 @@
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>of minus the same measure at offset before the anchor.</t>
+          <t>of minus the same measure at offset before the anchor. Source is a base or shiftable measure.</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11864,7 +11947,7 @@
       <c r="D32" s="5" t="inlineStr"/>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>growth_pct(of, lagged of) at offset. Same scale as fn growth_pct.</t>
+          <t>growth_pct(of, lagged of) at offset. Source is a base or shiftable measure. Same scale as fn growth_pct.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">

--- a/docs/KPI-Engine-Capabilities.xlsx
+++ b/docs/KPI-Engine-Capabilities.xlsx
@@ -749,7 +749,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Live allowlist from udfs/kpi_engine/registries/. YAML may only name what is listed here. Generated for authors, architects, and leadership.</t>
+          <t>Live allowlist from kpi_engine/registries/. YAML may only name what is listed here. Generated for authors, architects, and leadership.</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>If nothing matches: new catalog name, not core/</t>
+          <t>If nothing matches: new catalog name, not pipeline/</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Copy the pattern into config/kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml</t>
+          <t>Copy the pattern into kpi_config/kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>If no pattern fits, add a catalog name — do not edit core/</t>
+          <t>If no pattern fits, add a catalog name — do not edit pipeline/</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Host entry: udfs.kpi_engine.main   |   Routing: execution.kpi_id → config/kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml   |   AI brief: attach YAML preparation + catalogs + calculation intake (kpi-yaml-preparation-guide.md §0).</t>
+          <t>Host entry: kpi_engine.main   |   YAML root: KPI_ENGINE_CONFIG_DIR or sibling kpi_config/   |   Routing: execution.kpi_id → kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml   |   AI brief: attach YAML preparation + catalogs + calculation intake (kpi-yaml-preparation-guide.md §0).</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Copy config/kpis/sotif/3004.yaml → &lt;kpi_group&gt;/&lt;kpi_id&gt;.yaml. Fill time, dimensions, base_measures, cuts, measures. Host module_path stays udfs.kpi_engine.main.</t>
+          <t>Copy kpi_config/kpis/sotif/3004.yaml → &lt;kpi_group&gt;/&lt;kpi_id&gt;.yaml. Fill time, dimensions, base_measures, cuts, measures. Host module_path stays kpi_engine.main.</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>udfs/config/kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml</t>
+          <t>kpi_config/kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Do not add udfs/&lt;kpi&gt;.py. Do not edit core/.</t>
+          <t>Do not add a per-KPI Python module. Do not edit pipeline/.</t>
         </is>
       </c>
     </row>
@@ -6701,12 +6701,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Add config/models/&lt;kpi_group&gt;/&lt;id&gt;.yaml (kind: physical or sql). Point KPI model: at model_id. Paths stay on context.datasets.</t>
+          <t>Add kpi_config/models/&lt;kpi_group&gt;/&lt;id&gt;.yaml (kind: physical or sql). Point KPI model: at model_id. Paths stay on context.datasets.</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>udfs/config/models/&lt;kpi_group&gt;/&lt;id&gt;.yaml</t>
+          <t>kpi_config/models/&lt;kpi_group&gt;/&lt;id&gt;.yaml</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Not a core/ edit. KPI YAML uses op: &lt;new_name&gt;.</t>
+          <t>Not a pipeline/ edit. KPI YAML uses op: &lt;new_name&gt;.</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>kpi_engine/core/ + contracts.py</t>
+          <t>kpi_engine/pipeline/ + contracts.py</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>core/filter_ops.py</t>
+          <t>pipeline/filter_ops.py</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>After any registry change, regenerate udfs/kpi_engine/registries/CAPABILITIES.md (write_generated_docs).</t>
+          <t>After any registry change, regenerate kpi_engine/registries/CAPABILITIES.md (write_generated_docs).</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>config/kpis/&lt;kpi_group&gt;/&lt;kpi_id&gt;.yaml (or flat kpis/&lt;kpi_id&gt;.yaml)</t>
+          <t>kpi_config/kpis/&lt;kpi_group&gt;/&lt;kpi_id&gt;.yaml (or flat kpis/&lt;kpi_id&gt;.yaml)</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>config/models/&lt;kpi_group&gt;/&lt;id&gt;.yaml  —  KPI model: pointer</t>
+          <t>kpi_config/models/&lt;kpi_group&gt;/&lt;id&gt;.yaml  —  KPI model: pointer</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -7422,14 +7422,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Extending the engine without editing core/.</t>
+          <t>Extending the engine without editing pipeline/.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="29" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>core/ (frozen pipeline)</t>
+          <t>pipeline/ (frozen pipeline)</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>udfs/kpi_engine/core/</t>
+          <t>kpi_engine/pipeline/</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Path: udfs/config/kpis/&lt;kpi_group&gt;/&lt;kpi_id&gt;.yaml or flat kpis/&lt;kpi_id&gt;.yaml. Stem equals execution.kpi_id exactly (no fold). kpi_id is unique across groups.</t>
+          <t>Path: kpi_config/kpis/&lt;kpi_group&gt;/&lt;kpi_id&gt;.yaml or flat kpis/&lt;kpi_id&gt;.yaml. Stem equals execution.kpi_id exactly (no fold). kpi_id is unique across groups.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Path: udfs/config/models/&lt;kpi_group&gt;/&lt;model_id&gt;.yaml or flat models/&lt;model_id&gt;.yaml. Prefer lowercase snake_case. Extension must be .yaml. model_id is unique across groups.</t>
+          <t>Path: kpi_config/models/&lt;kpi_group&gt;/&lt;model_id&gt;.yaml or flat models/&lt;model_id&gt;.yaml. Prefer lowercase snake_case. Extension must be .yaml. model_id is unique across groups.</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -8004,17 +8004,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>One generic entry: udfs.kpi_engine.main. Routing is execution.kpi_id → config/kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml (or flat kpis/&lt;id&gt;.yaml). Do not add a per-KPI Python module.</t>
+          <t>One generic entry: kpi_engine.main. Routing is execution.kpi_id → kpi_config/kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml (or flat kpis/&lt;id&gt;.yaml). Do not add a per-KPI Python module.</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Host module_path: udfs.kpi_engine.main. New KPI = new YAML (+ model YAML if the extract is new).</t>
+          <t>Host module_path: kpi_engine.main. New KPI = new YAML (+ model YAML if the extract is new).</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>udfs/&lt;kpi_id&gt;/main.py. Cloning the engine per metric. A second module_path per kpi_id.</t>
+          <t>kpi_engine/&lt;kpi_id&gt;/main.py. Cloning the engine per metric. A second module_path per kpi_id.</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>See udfs/config/kpis/sotif/3004.yaml and udfs/config/models/sotif/sotif.yaml headers.</t>
+          <t>See kpi_config/kpis/sotif/3004.yaml and kpi_config/models/sotif/sotif.yaml headers.</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>See Naming conventions. .yaml only. Host module_path stays udfs.kpi_engine.main.</t>
+          <t>See Naming conventions. .yaml only. Host module_path stays kpi_engine.main.</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Inventing op: my_yoy. eval() in YAML. A new udfs/&lt;kpi&gt;.py. Editing core/.</t>
+          <t>Inventing op: my_yoy. eval() in YAML. A per-KPI Python module. Editing pipeline/.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>See gold file udfs/config/kpis/sotif/3004.yaml — copy structure, not Sotif names, unless this KPI is Sotif.</t>
+          <t>See gold file kpi_config/kpis/sotif/3004.yaml — copy structure, not Sotif names, unless this KPI is Sotif.</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Editing core/ per KPI</t>
+          <t>Editing pipeline/ per KPI</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">

--- a/docs/KPI-Engine-Capabilities.xlsx
+++ b/docs/KPI-Engine-Capabilities.xlsx
@@ -270,8 +270,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="All_operations" displayName="All_operations" ref="A1:E30" headerRowCount="1">
-  <autoFilter ref="A1:E30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="All_operations" displayName="All_operations" ref="A1:E32" headerRowCount="1">
+  <autoFilter ref="A1:E32"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Category"/>
     <tableColumn id="2" name="Operation"/>
@@ -5240,7 +5240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Bucket of the time column. Fiscal calendar only for Q/Y.</t>
+          <t>Bucket of the time column. Fiscal calendar only for Q/Y. Week is ISO-only.</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -5724,20 +5724,24 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>point offset</t>
+          <t>periods year/quarter/month/week/day</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Same measure at calendar offset from anchor.</t>
+          <t>Independent predicates. Selection S = matching grain buckets; anchor = max(S). Point folds S; windows/trends from anchor.</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>previous_year_value: { of: sotif_value, op: point, offset: { years: 1 } }</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
+          <t>time: { periods: { year: year, month: "current month" } }</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Cannot set with compose:. Finer than grain is a bind error.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="29" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -5747,17 +5751,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>window trailing / leading</t>
+          <t>point offset</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Inclusive trailing N (or leading) periods as one number.</t>
+          <t>Same measure over the (shifted) selection. Year-only + years:1 is the full prior year.</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>value_3m: { of: sotif_value, op: window, trailing: { months: 3 }, inclusive: true }</t>
+          <t>previous_year_value: { of: sotif_value, op: point, offset: { years: 1 } }</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
@@ -5770,22 +5774,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>window range</t>
+          <t>window trailing / leading</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>ytd, qtd, mtd, wtd, cumulative, full_month/quarter/year.</t>
+          <t>Inclusive trailing N (or leading) periods from anchor as one number.</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>value_qtd: { of: sotif_value, op: window, range: qtd }</t>
+          <t>value_3m: { of: sotif_value, op: window, trailing: { months: 3 }, inclusive: true }</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>wtd needs day grain</t>
+          <t>trailing: 3 from June is Apr-Jun</t>
         </is>
       </c>
     </row>
@@ -5797,22 +5801,22 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>trend</t>
+          <t>window range</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Fixed-length array + trend_axes / trend_labels. Cap 50,000 cells/cut.</t>
+          <t>ytd, qtd, mtd, wtd, cumulative, full_month/quarter/year. Named ranges are anchor-relative.</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>trend_12m: { of: sotif_value, op: trend, trailing: { months: 12 } }</t>
+          <t>value_qtd: { of: sotif_value, op: window, range: qtd }</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Defaults to default_cut only</t>
+          <t>mtd under year=2026 is December</t>
         </is>
       </c>
     </row>
@@ -5824,49 +5828,49 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>snapshot (omit time:)</t>
+          <t>trend</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>No month filter; all matching rows. Host reporting_month skipped as no_time.</t>
+          <t>Fixed-length array + trend_axes / trend_labels. Cap 50,000 cells/cut.</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Omit the time: block; only point offset 0 (and constants).</t>
+          <t>trend_12m: { of: sotif_value, op: trend, trailing: { months: 12 } }</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>No windows/trends/nonzero offsets</t>
+          <t>Defaults to default_cut only</t>
         </is>
       </c>
     </row>
     <row r="24" ht="29" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Cuts</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>group_by / ignore_filters / also_emit</t>
+          <t>snapshot (omit time:)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Named grains. G/R are examples, not hardcoded.</t>
+          <t>No month filter; all matching rows. Host reporting_month skipped as no_time.</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>cuts: [{ name: G, group_by: [], ignore_filters: [region], also_emit: [R] }]</t>
+          <t>Omit the time: block; only point offset 0 (and constants).</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>selected_dimensions overlays request grain</t>
+          <t>No windows/trends/nonzero offsets</t>
         </is>
       </c>
     </row>
@@ -5878,22 +5882,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>having</t>
+          <t>group_by / ignore_filters / also_emit</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Drop groups that fail measure predicates. Optional then_group_by.</t>
+          <t>Named grains. G/R are examples, not hardcoded.</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>having: { predicates: [{ of: current_value, cmp: gt, value: 0 }] }</t>
+          <t>cuts: [{ name: G, group_by: [], ignore_filters: [region], also_emit: [R] }]</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>cmp: gt gte lt lte eq ne between</t>
+          <t>selected_dimensions overlays request grain</t>
         </is>
       </c>
     </row>
@@ -5905,124 +5909,178 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>green_when</t>
+          <t>output_cut / pack_also_emit</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Boolean green flag on survivors (above/below).</t>
+          <t>Context output_cut is the also_emit walk root. YAML default does not lock. pack_also_emit: false emits only that cut.</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>green_when: { of: current_value, above: 40 }</t>
+          <t>cuts: [{ name: G, also_emit: [R], pack_also_emit: false }]</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Does not drop rows</t>
+          <t>Declare parameters.output_cut to accept the overlay</t>
         </is>
       </c>
     </row>
     <row r="27" ht="29" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Cuts</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>apply extract / calc / result</t>
+          <t>having</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>DuckDB WHERE vs Pandas vs drop JSON rows.</t>
+          <t>Drop groups that fail measure predicates. Optional then_group_by.</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>filters: { region: { apply: extract } }</t>
+          <t>having: { predicates: [{ of: current_value, cmp: gt, value: 0 }] }</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Unmapped valued filters are FilterError</t>
+          <t>cmp: gt gte lt lte eq ne between</t>
         </is>
       </c>
     </row>
     <row r="28" ht="29" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Multi-model</t>
+          <t>Cuts</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>model_relations</t>
+          <t>green_when</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Join two extracts on declared keys.</t>
+          <t>Boolean green flag on survivors (above/below).</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>model_relations: [{ left: a, right: b, on: [event_month, region], how: left }]</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr"/>
+          <t>green_when: { of: current_value, above: 40 }</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Does not drop rows</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="29" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Filters</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>identity_grain</t>
+          <t>apply extract / calc / result</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Helpers as measures.of only when every emitted cut equals this grain.</t>
+          <t>DuckDB WHERE vs Pandas vs drop JSON rows.</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>identity_grain: [carrier_id, shipment_id]</t>
+          <t>filters: { region: { apply: extract } }</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Otherwise BindError; fold with agg:</t>
+          <t>Unmapped valued filters are FilterError</t>
         </is>
       </c>
     </row>
     <row r="30" ht="29" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>Multi-model</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>model_relations</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Join two extracts on declared keys.</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>model_relations: [{ left: a, right: b, on: [event_month, region], how: left }]</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="29" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>identity_grain</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Helpers as measures.of only when every emitted cut equals this grain.</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>identity_grain: [carrier_id, shipment_id]</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Otherwise BindError; fold with agg:</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="29" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>SQL model</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>kind: sql</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Shape extract with CTEs; walked columns must be in output_schema.</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>models/&lt;id&gt;.yaml kind: sql + sql: + output_schema:</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Not KPI sql: formulas</t>
         </is>
@@ -7273,7 +7331,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>G/R are examples. group_by, ignore_filters, also_emit. Request grain overlays selected_dimensions.</t>
+          <t>G/R are examples. group_by, ignore_filters, also_emit, pack_also_emit. Request grain overlays selected_dimensions. Context output_cut is the walk root.</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -7285,7 +7343,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Global avg is recomputed, never mean of regional avgs.</t>
+          <t>Global avg is recomputed, never mean of regional avgs. YAML default for output_cut does not lock.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -7955,17 +8013,17 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>filter_code: reporting_month. filter_map: { "Supplier Name": supplier_name }.</t>
+          <t>filter_code: reporting_month. periods: { year: year, month: "current month" }. filter_map: { "Supplier Name": supplier_name }.</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>filter_map values with spaces or hyphens. Omitting filter_code when time: is present.</t>
+          <t>filter_map values with spaces or hyphens. Setting periods: and compose: together.</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>time.filter_code is required when time: is declared. It names the context filter that carries the selected period (the anchor), not a month IN list.</t>
+          <t>time.filter_code is required unless periods: or compose: is set. A scalar filter_code on the context still wins (one period, not a month IN list). periods: parts are independent predicates.</t>
         </is>
       </c>
     </row>
@@ -8217,22 +8275,22 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Either time.column + grain (day|week|month|quarter|year) + filter_code, or snapshot: true (omit time:).</t>
+          <t>Either time.column + grain (day|week|month|quarter|year) plus filter_code and/or periods:, or snapshot: true (omit time:).</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>time: { column: event_month, grain: month, filter_code: reporting_month, calendar: gregorian }.</t>
+          <t>time: { column: event_month, grain: month, periods: { year: year, month: "current month" }, calendar: gregorian }.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Guessing reporting_month. execution.time_grain. Two values as a range. Defaulting to 'latest' when the filter is missing.</t>
+          <t>Guessing reporting_month. execution.time_grain. Setting periods: and compose: together. A part finer than time.grain.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>The time filter is the anchor (exactly one value), never WHERE month IN (one month). Snapshot forbids window/trend/nonzero offset.</t>
+          <t>Scalar filter_code on the context is one value and wins. periods: parts conjoin (year alone = full year). Missing parts probe history. Snapshot forbids window/trend/nonzero offset.</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8302,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>dimensions (name + from physical column). default_dimensions (required, [] = worldwide). At least one cut. default_cut.</t>
+          <t>dimensions (name + from physical column). default_dimensions (required, [] = worldwide). At least one cut. default_cut. output_cut is a walk root (pack_also_emit: false locks one cut).</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -10508,7 +10566,7 @@
       <c r="D2" s="5" t="inlineStr"/>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Value at the selected period, optional calendar offset.</t>
+          <t>Value over the time selection (one bucket or many), optional calendar offset.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -11371,7 +11429,7 @@
       <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Value of a base or shiftable measure at offset before the anchor.</t>
+          <t>Value of a base or shiftable measure over the selection shifted by offset.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -11419,7 +11477,7 @@
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Value of a base or shiftable measure at offset after the anchor.</t>
+          <t>Value of a base or shiftable measure over the selection shifted forward by offset.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -11467,7 +11525,7 @@
       <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>of / lagged of × 100. Source is a base or shiftable measure. 100 means unchanged vs the offset period.</t>
+          <t>of / lagged of × 100 over the selection vs the shifted selection. Source is a base or shiftable measure. 100 means unchanged.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -11899,7 +11957,7 @@
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>of minus the same measure at offset before the anchor. Source is a base or shiftable measure.</t>
+          <t>of minus the same measure over the selection shifted by offset. Source is a base or shiftable measure.</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11947,7 +12005,7 @@
       <c r="D32" s="5" t="inlineStr"/>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>growth_pct(of, lagged of) at offset. Source is a base or shiftable measure. Same scale as fn growth_pct.</t>
+          <t>growth_pct(of, lagged of) over the selection vs the shifted selection. Source is a base or shiftable measure. Same scale as fn growth_pct.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">

--- a/docs/KPI-Engine-Capabilities.xlsx
+++ b/docs/KPI-Engine-Capabilities.xlsx
@@ -250,8 +250,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Hooks" displayName="Hooks" ref="A1:K20" headerRowCount="1">
-  <autoFilter ref="A1:K20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Hooks" displayName="Hooks" ref="A1:K22" headerRowCount="1">
+  <autoFilter ref="A1:K22"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Role"/>
@@ -270,8 +270,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="All_operations" displayName="All_operations" ref="A1:E32" headerRowCount="1">
-  <autoFilter ref="A1:E32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="All_operations" displayName="All_operations" ref="A1:E33" headerRowCount="1">
+  <autoFilter ref="A1:E33"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Category"/>
     <tableColumn id="2" name="Operation"/>
@@ -4197,7 +4197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4482,7 +4482,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>rolling_median</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Median of period values in the trailing window.</t>
@@ -5225,6 +5229,105 @@
       </c>
       <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="81" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>mad</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Median absolute deviation of period values in the trailing window.</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>robust_spread:
+  op: hook
+  hook: mad
+  of: sotif_value
+  trailing: { months: 12 }</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>mad</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="94" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Linear forecast — last observed value plus slope times periods_ahead (default 1).</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>next_month:
+  op: hook
+  hook: projection
+  of: sotif_value
+  trailing: { months: 12 }
+  periods_ahead: 1</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5240,7 +5343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5358,7 +5461,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="29" customHeight="1">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Row helper</t>
@@ -5371,17 +5474,18 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Pandas row mask before fold. Numeric ops coerce the compare column. ne excludes nulls (SQL-style).</t>
+          <t>Pandas row mask before fold. Also legal on a measure whose of: is a base (clone). Numeric ops coerce the compare column. ne excludes nulls (SQL-style).</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>where: { column: mrr, op: gt, value: 0 }</t>
+          <t>where: { column: mrr, op: gt, value: 0 }
+measures.late: { of: fact, op: point, where: { column: status, op: eq, value: LATE } }</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Ops: in eq ne gt gte lt lte between. between needs values: [lo, hi]. Not like/is_null.</t>
+          <t>Ops: in eq ne gt gte lt lte between. between needs values: [lo, hi]. Not like/is_null. ignore_filters: on a measure skips context codes.</t>
         </is>
       </c>
     </row>
@@ -5470,49 +5574,49 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>first / last</t>
+          <t>stddev / variance / mode</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Identity fold after sort by time (or window). Text columns are still coerced to numeric.</t>
+          <t>Non-additive sample stdev/var (ddof=1). One row → null. mode ties → smallest.</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>base_measures.bal: { sql: balance, agg: last }</t>
+          <t>base_measures.spread: { sql: amount, agg: stddev }</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Used with over: last_n</t>
+          <t>Same path as median</t>
         </is>
       </c>
     </row>
     <row r="10" ht="29" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Row helper</t>
+          <t>Aggregation</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>expr</t>
+          <t>first / last</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Named row formula on columns or earlier helpers. No DuckDB SUM().</t>
+          <t>Identity fold after sort by time (or window). Text columns are still coerced to numeric.</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>gross: { expr: qty * price }</t>
+          <t>base_measures.bal: { sql: balance, agg: last }</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Add agg: to fold, or identity_grain for point of</t>
+          <t>Used with over: last_n</t>
         </is>
       </c>
     </row>
@@ -5524,20 +5628,24 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>lookup</t>
+          <t>expr</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Map a column through a dict; default or strict.</t>
+          <t>Named row formula on columns or earlier helpers. No DuckDB SUM().</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>fee: { lookup: { column: pay, map: { COD: 25 }, default: 10 } }</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
+          <t>gross: { expr: qty * price }</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Add agg: to fold, or identity_grain for point of</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="29" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -5547,17 +5655,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>sql: column</t>
+          <t>lookup</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Pass a physical column (or simple ident). Default agg is sum if omitted.</t>
+          <t>Map a column through a dict; default or strict.</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>sotif_value: { sql: amount, agg: sum }</t>
+          <t>fee: { lookup: { column: pay, map: { COD: 25 }, default: 10 } }</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
@@ -5570,49 +5678,45 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>columns + op</t>
+          <t>sql: column</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Call a column function by name.</t>
+          <t>Pass a physical column (or simple ident). Default agg is sum if omitted.</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>ontime_full: { columns: [ontime, fullqty], op: multiply, agg: sum }</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>See Column functions sheet</t>
-        </is>
-      </c>
+          <t>sotif_value: { sql: amount, agg: sum }</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="29" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Entity window</t>
+          <t>Row helper</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>over.lag / lead</t>
+          <t>columns + op</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Value from another row in partition, ordered by order_by. Requires of:.</t>
+          <t>Call a column function by name.</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>prev: { over: { fn: lag, of: order_date, partition_by: [customer_id], order_by: [order_date] }, agg: max }</t>
+          <t>ontime_full: { columns: [ontime, fullqty], op: multiply, agg: sum }</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Not calendar op: lag</t>
+          <t>See Column functions sheet</t>
         </is>
       </c>
     </row>
@@ -5624,20 +5728,24 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>over.row_number / rank / dense_rank</t>
+          <t>over.lag / lead</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Sequence in partition. of: optional.</t>
+          <t>Value from another row in partition, ordered by order_by. Requires of:.</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>seq: { over: { fn: row_number, partition_by: [customer_id], order_by: [order_date] }, agg: max }</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
+          <t>prev: { over: { fn: lag, of: order_date, partition_by: [customer_id], order_by: [order_date] }, agg: max }</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Not calendar op: lag</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="29" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -5647,17 +5755,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>over.running_sum / running_avg</t>
+          <t>over.row_number / rank / dense_rank</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Running aggregate along order_by. Requires of:.</t>
+          <t>Sequence in partition. of: optional.</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>run: { over: { fn: running_sum, of: net, partition_by: [carrier_id], order_by: [start] }, agg: max }</t>
+          <t>seq: { over: { fn: row_number, partition_by: [customer_id], order_by: [order_date] }, agg: max }</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr"/>
@@ -5670,49 +5778,45 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>over.last_n</t>
+          <t>over.running_sum / running_avg</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>JSON list of last n of values. Point only; cannot feed arithmetic.</t>
+          <t>Running aggregate along order_by. Requires of:.</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>recent: { over: { fn: last_n, of: amount, n: 2, partition_by: [region], order_by: [order_id] }, agg: last }</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Dates as ISO strings</t>
-        </is>
-      </c>
+          <t>run: { over: { fn: running_sum, of: net, partition_by: [carrier_id], order_by: [start] }, agg: max }</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="29" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Entity window</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>grain day/week/month/quarter/year</t>
+          <t>over.last_n</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Bucket of the time column. Fiscal calendar only for Q/Y. Week is ISO-only.</t>
+          <t>JSON list of last n of values. Point only; cannot feed arithmetic.</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>time: { column: event_month, grain: month, filter_code: reporting_month }</t>
+          <t>recent: { over: { fn: last_n, of: amount, n: 2, partition_by: [region], order_by: [order_id] }, agg: last }</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>parameters.time_grain overlay if declared</t>
+          <t>Dates as ISO strings</t>
         </is>
       </c>
     </row>
@@ -5724,22 +5828,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>periods year/quarter/month/week/day</t>
+          <t>grain day/week/month/quarter/year</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Independent predicates. Selection S = matching grain buckets; anchor = max(S). Point folds S; windows/trends from anchor.</t>
+          <t>Bucket of the time column. Fiscal calendar only for Q/Y. Week is ISO-only.</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>time: { periods: { year: year, month: "current month" } }</t>
+          <t>time: { column: event_month, grain: month, filter_code: reporting_month }</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Cannot set with compose:. Finer than grain is a bind error.</t>
+          <t>parameters.time_grain overlay if declared</t>
         </is>
       </c>
     </row>
@@ -5751,20 +5855,24 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>point offset</t>
+          <t>periods year/quarter/month/week/day</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Same measure over the (shifted) selection. Year-only + years:1 is the full prior year.</t>
+          <t>Independent predicates. Selection S = matching grain buckets; anchor = max(S). Point folds S; windows/trends from anchor.</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>previous_year_value: { of: sotif_value, op: point, offset: { years: 1 } }</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
+          <t>time: { periods: { year: year, month: "current month" } }</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Cannot set with compose:. Finer than grain is a bind error.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="29" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -5774,24 +5882,20 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>window trailing / leading</t>
+          <t>point offset</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Inclusive trailing N (or leading) periods from anchor as one number.</t>
+          <t>Same measure over the (shifted) selection. Year-only + years:1 is the full prior year.</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>value_3m: { of: sotif_value, op: window, trailing: { months: 3 }, inclusive: true }</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>trailing: 3 from June is Apr-Jun</t>
-        </is>
-      </c>
+          <t>previous_year_value: { of: sotif_value, op: point, offset: { years: 1 } }</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
     </row>
     <row r="22" ht="29" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -5801,22 +5905,22 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>window range</t>
+          <t>window trailing / leading</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>ytd, qtd, mtd, wtd, cumulative, full_month/quarter/year. Named ranges are anchor-relative.</t>
+          <t>Inclusive trailing N (or leading) periods from anchor as one number.</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>value_qtd: { of: sotif_value, op: window, range: qtd }</t>
+          <t>value_3m: { of: sotif_value, op: window, trailing: { months: 3 }, inclusive: true }</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>mtd under year=2026 is December</t>
+          <t>trailing: 3 from June is Apr-Jun</t>
         </is>
       </c>
     </row>
@@ -5828,22 +5932,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>trend</t>
+          <t>window range</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Fixed-length array + trend_axes / trend_labels. Cap 50,000 cells/cut.</t>
+          <t>ytd, qtd, mtd, wtd, cumulative, full_month/quarter/year. Named ranges are anchor-relative.</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>trend_12m: { of: sotif_value, op: trend, trailing: { months: 12 } }</t>
+          <t>value_qtd: { of: sotif_value, op: window, range: qtd }</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Defaults to default_cut only</t>
+          <t>mtd under year=2026 is December</t>
         </is>
       </c>
     </row>
@@ -5855,49 +5959,49 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>snapshot (omit time:)</t>
+          <t>trend</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>No month filter; all matching rows. Host reporting_month skipped as no_time.</t>
+          <t>Fixed-length array + trend_axes / trend_labels. Cap 50,000 cells/cut.</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Omit the time: block; only point offset 0 (and constants).</t>
+          <t>trend_12m: { of: sotif_value, op: trend, trailing: { months: 12 } }</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>No windows/trends/nonzero offsets</t>
+          <t>Defaults to default_cut only</t>
         </is>
       </c>
     </row>
     <row r="25" ht="29" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Cuts</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>group_by / ignore_filters / also_emit</t>
+          <t>snapshot (omit time:)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Named grains. G/R are examples, not hardcoded.</t>
+          <t>No month filter; all matching rows. Host reporting_month skipped as no_time.</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>cuts: [{ name: G, group_by: [], ignore_filters: [region], also_emit: [R] }]</t>
+          <t>Omit the time: block; only point offset 0 (and constants).</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>selected_dimensions overlays request grain</t>
+          <t>No windows/trends/nonzero offsets</t>
         </is>
       </c>
     </row>
@@ -5909,22 +6013,22 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>output_cut / pack_also_emit</t>
+          <t>group_by / ignore_filters / also_emit</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Context output_cut is the also_emit walk root. YAML default does not lock. pack_also_emit: false emits only that cut.</t>
+          <t>Named grains. G/R are examples, not hardcoded.</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>cuts: [{ name: G, also_emit: [R], pack_also_emit: false }]</t>
+          <t>cuts: [{ name: G, group_by: [], ignore_filters: [region], also_emit: [R] }]</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Declare parameters.output_cut to accept the overlay</t>
+          <t>selected_dimensions overlays request grain</t>
         </is>
       </c>
     </row>
@@ -5936,22 +6040,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>having</t>
+          <t>output_cut / pack_also_emit</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Drop groups that fail measure predicates. Optional then_group_by.</t>
+          <t>Context output_cut is the also_emit walk root. YAML default does not lock. pack_also_emit: false emits only that cut.</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>having: { predicates: [{ of: current_value, cmp: gt, value: 0 }] }</t>
+          <t>cuts: [{ name: G, also_emit: [R], pack_also_emit: false }]</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>cmp: gt gte lt lte eq ne between</t>
+          <t>Declare parameters.output_cut to accept the overlay</t>
         </is>
       </c>
     </row>
@@ -5963,124 +6067,151 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>green_when</t>
+          <t>having</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Boolean green flag on survivors (above/below).</t>
+          <t>Drop groups that fail measure predicates. Optional then_group_by.</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>green_when: { of: current_value, above: 40 }</t>
+          <t>having: { predicates: [{ of: current_value, cmp: gt, value: 0 }] }</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Does not drop rows</t>
+          <t>cmp: gt gte lt lte eq ne between</t>
         </is>
       </c>
     </row>
     <row r="29" ht="29" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Cuts</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>apply extract / calc / result</t>
+          <t>green_when</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>DuckDB WHERE vs Pandas vs drop JSON rows.</t>
+          <t>Boolean green flag on survivors (above/below).</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>filters: { region: { apply: extract } }</t>
+          <t>green_when: { of: current_value, above: 40 }</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Unmapped valued filters are FilterError</t>
+          <t>Does not drop rows</t>
         </is>
       </c>
     </row>
     <row r="30" ht="29" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Multi-model</t>
+          <t>Filters</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>model_relations</t>
+          <t>apply extract / calc / result</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Join two extracts on declared keys.</t>
+          <t>DuckDB WHERE vs Pandas vs drop JSON rows.</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>model_relations: [{ left: a, right: b, on: [event_month, region], how: left }]</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr"/>
+          <t>filters: { region: { apply: extract } }</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Unmapped valued filters are FilterError</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="29" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Multi-model</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>identity_grain</t>
+          <t>model_relations</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Helpers as measures.of only when every emitted cut equals this grain.</t>
+          <t>Join two extracts on declared keys.</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>identity_grain: [carrier_id, shipment_id]</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Otherwise BindError; fold with agg:</t>
-        </is>
-      </c>
+          <t>model_relations: [{ left: a, right: b, on: [event_month, region], how: left }]</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
     </row>
     <row r="32" ht="29" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>identity_grain</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Helpers as measures.of only when every emitted cut equals this grain.</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>identity_grain: [carrier_id, shipment_id]</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Otherwise BindError; fold with agg:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="29" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
           <t>SQL model</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>kind: sql</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Shape extract with CTEs; walked columns must be in output_schema.</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>models/&lt;id&gt;.yaml kind: sql + sql: + output_schema:</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Not KPI sql: formulas</t>
         </is>
@@ -8356,7 +8487,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>SUM/COUNT/MIN/MAX of a column at the selected period.</t>
+          <t>SUM/COUNT/MIN/MAX of a column over the time selection (one bucket or many).</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -8372,7 +8503,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>agg: sum | avg | count | count_distinct | min | max | median | percentile | first | last.</t>
+          <t>agg: sum | avg | count | count_distinct | min | max | median | percentile | first | last | stddev | variance | mode.</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8515,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Same metric last year/month/quarter; growth % vs that period.</t>
+          <t>Same metric last year/month/quarter over the shifted selection; growth % vs that set (year-only is year vs year).</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -8423,12 +8554,12 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>lag of trend/hook/rank. lag of a row helper (no agg:).</t>
+          <t>lag of trend/rank. lag of a row helper (no agg:). Rank a lagged measure instead of lagging a rank. Put offset: on the trend.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Sources: bases and shiftable measures (point, window, fn, expr, …).</t>
+          <t>Sources: bases and shiftable measures (point, window, fn, expr, hook, …).</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8929,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>seasonal_index, ewma, period_max, period_min, period_median, period_avg, period_sum, hit_rate, streak, period_stdev, period_var, period_cv, period_range, period_count, miss_rate, miss_streak, longest_streak, cagr, slope</t>
+          <t>seasonal_index, ewma, period_max, period_min, period_median, period_avg, period_sum, hit_rate, streak, period_stdev, period_var, period_cv, period_range, period_count, miss_rate, miss_streak, longest_streak, cagr, slope, mad, projection</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -9146,7 +9277,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>op: percent_of_total (optional partition_by)</t>
+          <t>op: percent_of_total (optional partition_by, versus_cut)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -10242,7 +10373,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="68" customHeight="1">
+    <row r="6" ht="133" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>5. Share of worldwide (cut op)</t>
@@ -10263,7 +10394,12 @@
           <t>measures:
   group_share:
     op: percent_of_total
-    of: current_value</t>
+    of: current_value
+  vs_global:
+    op: percent_of_total
+    of: current_value
+    versus_cut: G
+    cuts: [R]</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">

--- a/docs/KPI-Engine-Capabilities.xlsx
+++ b/docs/KPI-Engine-Capabilities.xlsx
@@ -837,7 +837,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>kpi-yaml-preparation-guide.md §0 — do not invent ops; ask if intake is incomplete</t>
+          <t>kpi-yaml-ai-prep.md — do not invent ops; ask if intake is incomplete</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Host entry: kpi_engine.main   |   YAML root: KPI_ENGINE_CONFIG_DIR or sibling kpi_config/   |   Routing: execution.kpi_id → kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml   |   AI brief: attach YAML preparation + catalogs + calculation intake (kpi-yaml-preparation-guide.md §0).</t>
+          <t>Host entry: kpi_engine.main   |   YAML root: KPI_ENGINE_CONFIG_DIR or sibling kpi_config/   |   Routing: execution.kpi_id → kpis/&lt;kpi_group&gt;/&lt;id&gt;.yaml   |   AI brief: attach kpi-yaml-ai-prep.md + catalogs + calculation intake.</t>
         </is>
       </c>
     </row>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Attach this workbook (Naming conventions, this sheet, Measure ops, Column/Measure functions, Hooks, YAML patterns) plus kpi-yaml-preparation-guide.md §0 plus a filled intake.</t>
+          <t>Attach this workbook (Naming conventions, this sheet, Measure ops, Column/Measure functions, Hooks, YAML patterns) plus kpi-yaml-ai-prep.md plus a filled intake.</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Emit YAML only when every box is true (same list as kpi-yaml-preparation-guide.md §0.7).</t>
+          <t>Emit YAML only when every box is true (same list as kpi-yaml-ai-prep.md §8).</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">

--- a/docs/KPI-Engine-Capabilities.xlsx
+++ b/docs/KPI-Engine-Capabilities.xlsx
@@ -230,8 +230,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Measure_functions" displayName="Measure_functions" ref="A1:K32" headerRowCount="1">
-  <autoFilter ref="A1:K32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Measure_functions" displayName="Measure_functions" ref="A1:K42" headerRowCount="1">
+  <autoFilter ref="A1:K42"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Role"/>
@@ -250,8 +250,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Hooks" displayName="Hooks" ref="A1:K22" headerRowCount="1">
-  <autoFilter ref="A1:K22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Hooks" displayName="Hooks" ref="A1:K37" headerRowCount="1">
+  <autoFilter ref="A1:K37"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Role"/>
@@ -399,8 +399,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Measure_ops" displayName="Measure_ops" ref="A1:K32" headerRowCount="1">
-  <autoFilter ref="A1:K32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Measure_ops" displayName="Measure_ops" ref="A1:K59" headerRowCount="1">
+  <autoFilter ref="A1:K59"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Role"/>
@@ -419,8 +419,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Column_functions" displayName="Column_functions" ref="A1:K29" headerRowCount="1">
-  <autoFilter ref="A1:K29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Column_functions" displayName="Column_functions" ref="A1:K47" headerRowCount="1">
+  <autoFilter ref="A1:K47"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Role"/>
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2562,6 +2562,858 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr"/>
     </row>
+    <row r="30" ht="55" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>weighted_product</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Row-wise product of columns.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>wp:
+  columns: [qty, price]
+  op: weighted_product</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>weighted_product_columns</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="55" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>safe_divide</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Numerator / denominator; zero denominator is null.</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>rate:
+  columns: [shipped, ordered]
+  op: safe_divide</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>safe_divide_columns</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="55" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>clip</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Clamp value into [lo, hi].</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>capped:
+  columns: [amount, lo, hi]
+  op: clip</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>clip_columns</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="55" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>parse_date</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Parse a column as a timestamp.</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>dt:
+  columns: [date_text]
+  op: parse_date</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>parse_date_columns</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="55" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>parse_number</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Parse a column as a float.</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>n:
+  columns: [amount_text]
+  op: parse_number</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>parse_number_columns</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="55" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>trim</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Strip whitespace.</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>clean:
+  columns: [region]
+  op: trim</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>trim_columns</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="55" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Uppercase.</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>up:
+  columns: [region]
+  op: upper</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>upper_columns</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="55" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Lowercase.</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>lo:
+  columns: [region]
+  op: lower</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>lower_columns</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>substring</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Slice text from start for length (0-based).</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>code:
+  expr: "substring(reason_code, 0, 4)"</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>substring_columns</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Left n characters.</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>prefix:
+  expr: "left(reason_code, 4)"</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>left_columns</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Right n characters.</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>suffix:
+  expr: "right(reason_code, 2)"</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>right_columns</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Replace old with new in a string column.</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>swapped:
+  expr: "replace(region, 'NA', 'US')"</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>replace_columns</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>concat</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Concatenate string columns.</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>label:
+  expr: "concat(region, reason_code)"</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>concat_columns</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>hash_bucket</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Stable 0..n-1 bucket from the value.</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>bucket:
+  expr: "hash_bucket(supplier_name, 10)"</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>hash_bucket_columns</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>json_extract</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Pandas JSON path extract on a string column.</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>field:
+  expr: "json_extract(payload, '$.a')"</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>json_extract_columns</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="55" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>coalesce_date</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>First non-null parseable date.</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>when:
+  columns: [ship_date, order_date]
+  op: coalesce_date</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>coalesce_date_columns</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46" ht="55" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>is_between_dates</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>1 if value is in [start, end].</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>in_range:
+  columns: [event_month, start_date, end_date]
+  op: is_between_dates</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>is_between_dates_columns</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>flag_in_set</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>1 if value equals any following argument.</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>is_na:
+  expr: "flag_in_set(region, 'NA', 'EU')"</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Use in base_measures with columns: + op:, or inside expr:/sql: as name(...). Then fold with agg:. These run per retrieved row, not on totals.</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.column.impl</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>flag_in_set_columns</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -2576,7 +3428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4183,6 +5035,502 @@
       <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="5" t="inlineStr"/>
     </row>
+    <row r="33" ht="68" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>geomean_scalars</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Geometric mean of positive measure scalars.</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>g:
+  op: fn
+  fn: geomean_scalars
+  inputs: [a, b]</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>geomean_scalars</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="68" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>weighted_avg_scalars</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Weighted average of (value, weight) pairs.</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>w:
+  op: fn
+  fn: weighted_avg_scalars
+  inputs: [a, wa, b, wb]</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>weighted_avg_scalars</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="68" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>harmonic_mean</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>harmonic_mean_scalars</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Harmonic mean of positive scalars.</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>h:
+  op: fn
+  fn: harmonic_mean
+  inputs: [a, b]</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>harmonic_mean_scalars</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="68" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>min_max_spread</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>max - min of the inputs.</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>spread:
+  op: fn
+  fn: min_max_spread
+  inputs: [a, b]</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>min_max_spread</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="68" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>ratio_safe</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Numerator / denominator; zero denominator is null.</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>r:
+  op: fn
+  fn: ratio_safe
+  inputs: [a, b]</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>ratio_safe</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38" ht="68" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>bps_change</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Percent change in basis points.</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>bps:
+  op: fn
+  fn: bps_change
+  inputs: [current_value, previous]</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>bps_change</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="68" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>log_change</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>ln(current / previous).</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>lc:
+  op: fn
+  fn: log_change
+  inputs: [current_value, previous]</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>log_change</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="68" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>if_between</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>1 if value is in [lo, hi].</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>in_band:
+  op: fn
+  fn: if_between
+  inputs: [current_value, lo, hi]</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>if_between</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="68" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>all_null</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>1 if every input is null.</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>missing:
+  op: fn
+  fn: all_null
+  inputs: [a, b]</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>all_null</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42" ht="68" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>any_null</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>1 if any input is null.</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>some_missing:
+  op: fn
+  fn: any_null
+  inputs: [a, b]</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Use under measures with op: fn (fn: + inputs:), op: arithmetic, or op: expr. Inputs are other measure keys (already aggregated). Not physical columns.</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.functions.measure.impl</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>any_null</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -4197,7 +5545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5328,6 +6676,750 @@
       </c>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="81" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>autocorrelation</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Lag-1 Pearson correlation of consecutive observed period values.</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>ac1:
+  op: hook
+  hook: autocorrelation
+  of: sotif_value
+  trailing: { months: 12 }</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>autocorrelation</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="81" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>rsi</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Wilder RSI of period-to-period changes.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>rsi14:
+  op: hook
+  hook: rsi
+  of: sotif_value
+  trailing: { months: 14 }</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>rsi</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="94" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>bollinger</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>%b of the last value in a k-sigma band around the window mean (k default 2).</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>bb:
+  op: hook
+  hook: bollinger
+  of: sotif_value
+  trailing: { months: 12 }
+  k: 2</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>bollinger</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="94" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>exponential_decay_sum</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Sum v_i × decay^(age). decay default 0.5.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>decayed:
+  op: hook
+  hook: exponential_decay_sum
+  of: sotif_value
+  trailing: { months: 12 }
+  decay: 0.5</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>exponential_decay_sum</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="81" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>theil_sen_slope</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Median of pairwise slopes of value vs observed period index.</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>robust_slope:
+  op: hook
+  hook: theil_sen_slope
+  of: sotif_value
+  trailing: { months: 12 }</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>theil_sen_slope</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="81" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>1-based index of the mean-shift split in the trailing window.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>shift:
+  op: hook
+  hook: changepoint
+  of: sotif_value
+  trailing: { months: 12 }</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="81" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>outlier_count</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Count of observed values with |z| &gt; k (default 3).</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>outliers:
+  op: hook
+  hook: outlier_count
+  of: sotif_value
+  trailing: { months: 12 }</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>outlier_count</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="81" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>percentile_rank_series</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Percentile rank (0–100) of the last observed value in the window.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>pr:
+  op: hook
+  hook: percentile_rank_series
+  of: sotif_value
+  trailing: { months: 12 }</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>percentile_rank_series</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="94" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>weighted_ewma</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>EWMA with explicit alpha (default 2/(N+1)).</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>smooth:
+  op: hook
+  hook: weighted_ewma
+  of: sotif_value
+  trailing: { months: 12 }
+  alpha: 0.3</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>weighted_ewma</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="81" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>run_rate</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Last observed value annualized by the KPI grain.</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>annualized:
+  op: hook
+  hook: run_rate
+  of: sotif_value
+  trailing: { months: 3 }</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>run_rate</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="94" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>target_trajectory</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Last / linear path from first observed to value: target.</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>pace:
+  op: hook
+  hook: target_trajectory
+  of: sotif_value
+  trailing: { months: 12 }
+  value: 100</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>target_trajectory</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="94" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>forecast_confidence</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Linear projection ± k × stdev. Bind expands to {key}_low / {key}_high unless emit: names one side.</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>fc:
+  op: hook
+  hook: forecast_confidence
+  of: sotif_value
+  trailing: { months: 12 }
+  k: 1.96</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>forecast_confidence</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="81" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>seasonal_decompose</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Seasonal factor at the anchor month (same-month mean / overall mean).</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>seas:
+  op: hook
+  hook: seasonal_decompose
+  of: sotif_value
+  trailing: { months: 36 }</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>seasonal_decompose</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="107" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>cohort_retention</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Share of entities first seen at entry_period that are still present at the anchor.</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>retain:
+  op: hook
+  hook: cohort_retention
+  of: sotif_value
+  trailing: { months: 12 }
+  cohort_column: supplier_name
+  entry_period: "2025-01-01"</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>cohort_retention</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="107" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>survival_rate</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Share of entities that entered on or before entry_period still present at the anchor.</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>survive:
+  op: hook
+  hook: survival_rate
+  of: sotif_value
+  trailing: { months: 12 }
+  cohort_column: supplier_name
+  entry_period: "2025-01-01"</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>measures: { op: hook, hook: &lt;name&gt;, of: &lt;base&gt;, trailing: { months: N } }. Declare trailing/offset so required_span is wide enough. Hooks that list requires_value need value:.</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.hooks.impl</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>survival_rate</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8848,7 +10940,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>point, window, trend, arithmetic, fn, expr, constant, dimension, predicate, hook, rank, percent_of_total, ntile, dense_rank, row_number, cumulative_share, running_total, contribution, lag, lead, index, vs_target, threshold, percent_rank, gap_to_leader, gap_to_avg, zscore, running_avg, top_n, diff, pct_change</t>
+          <t>point, window, trend, trend_arithmetic, arithmetic, fn, expr, constant, dimension, predicate, hook, rank, percent_of_total, ntile, dense_rank, row_number, cumulative_share, running_total, contribution, lag, lead, index, vs_target, threshold, percent_rank, gap_to_leader, gap_to_avg, zscore, running_avg, top_n, diff, pct_change, compare, filtered_point, filtered_window, filtered_trend, filtered_compare, expanding_window, shifted_trend, rate, cumulative_point, n_period_avg, weighted_window, snapshot_compare, bottom_n, rank_pct_change, concentration, abc_class, pareto_flag, normalize, annualize, vs_prior_window, delta_contribution, baseline_index, band, envelope, compound_growth, seasonal_adjust</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -8875,7 +10967,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>value, abs, sum, subtract, multiply, divide, percent_of, min, max, avg, coalesce, if_null, nullif, null_if_zero, zero_if_null, is_null, is_not_null, if_else, round, floor, ceil, power, log, log10, sqrt, date_diff, date_add, epoch_day</t>
+          <t>value, abs, sum, subtract, multiply, divide, percent_of, min, max, avg, coalesce, if_null, nullif, null_if_zero, zero_if_null, is_null, is_not_null, if_else, round, floor, ceil, power, log, log10, sqrt, date_diff, date_add, epoch_day, weighted_product, safe_divide, clip, parse_date, parse_number, trim, upper, lower, substring, left, right, replace, concat, hash_bucket, json_extract, coalesce_date, is_between_dates, flag_in_set</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -8902,7 +10994,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>growth_pct, divide, percent, sum, subtract, multiply, min, max, avg, abs, clamp, attainment, coalesce, if_null, nullif, null_if_zero, zero_if_null, is_null, is_not_null, if_else, sign_label, round, floor, ceil, power, log, log10, sqrt, date_diff, date_add, epoch_day</t>
+          <t>growth_pct, divide, percent, sum, subtract, multiply, min, max, avg, abs, clamp, attainment, coalesce, if_null, nullif, null_if_zero, zero_if_null, is_null, is_not_null, if_else, sign_label, round, floor, ceil, power, log, log10, sqrt, date_diff, date_add, epoch_day, geomean_scalars, weighted_avg_scalars, harmonic_mean, min_max_spread, ratio_safe, bps_change, log_change, if_between, all_null, any_null</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -8929,7 +11021,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>seasonal_index, ewma, period_max, period_min, period_median, period_avg, period_sum, hit_rate, streak, period_stdev, period_var, period_cv, period_range, period_count, miss_rate, miss_streak, longest_streak, cagr, slope, mad, projection</t>
+          <t>seasonal_index, ewma, period_max, period_min, period_median, period_avg, period_sum, hit_rate, streak, period_stdev, period_var, period_cv, period_range, period_count, miss_rate, miss_streak, longest_streak, cagr, slope, mad, projection, autocorrelation, rsi, bollinger, exponential_decay_sum, theil_sen_slope, changepoint, outlier_count, percentile_rank_series, weighted_ewma, run_rate, target_trajectory, forecast_confidence, seasonal_decompose, cohort_retention, survival_rate</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -10610,7 +12702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10827,10 +12919,10 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
     </row>
-    <row r="5" ht="68" customHeight="1">
+    <row r="5" ht="94" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>trend_arithmetic</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -10846,10 +12938,60 @@
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>Per-period fn or expr over base totals or aligned trend series (ratio-of-totals, not a trend of a composite scalar).</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>sotif_pct_trend:
+  op: trend_arithmetic
+  of: [total_po, supplier_driven_po]
+  expr: (total_po - supplier_driven_po) / total_po
+  trailing: { months: 12 }
+  cuts: [G]</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>TrendArithmetic</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="68" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Combine other measures with a registered measure function (default divide).</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>ratio:
   op: arithmetic
@@ -10857,47 +12999,47 @@
   fn: divide</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.combo</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Arithmetic</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="68" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="68" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Feed other measures' scalars into a named measure function.</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>yoy:
   op: fn
@@ -10905,122 +13047,75 @@
   inputs: [current_value, previous_year_value]</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.combo</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Fn</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="55" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="55" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>expr</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Formula over other measures using + - * /.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>blended:
   op: expr
   expr: (current_value + previous_year_value) / 2</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.combo</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Expr</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>constant</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>A literal number on every row.</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>target:
-  op: constant
-  value: 95</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>kpi_engine.capabilities.ops.combo</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Constant</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr"/>
     </row>
-    <row r="9" ht="42" customHeight="1">
+    <row r="9" ht="81" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>dimension</t>
+          <t>constant</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -11036,56 +13131,105 @@
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
+          <t>A literal number, or a per-dimension map with default.</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>region_target:
+  op: constant
+  by: region
+  value: { APAC: 90, EMEA: 85 }
+  default: null</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>Echo a grouping field as a requestable measure key.</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>region:
   op: dimension</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.combo</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Dimension</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="94" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="94" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>predicate</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>1/0 flag when all (or any) measure predicates pass. Does not drop rows.</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>healthy:
   op: predicate
@@ -11095,47 +13239,47 @@
     - { of: return_rate, cmp: lt, value: 0.20 }</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.combo</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Predicate</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="68" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="68" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>hook</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Call an allowlisted Python hook for logic the catalog cannot express.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>custom:
   op: hook
@@ -11143,47 +13287,47 @@
   of: sotif_value</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.combo</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Hook</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="68" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="68" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Rank groups on a cut. Ties share a rank; the next rank skips.</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>reason_rank:
   op: rank
@@ -11191,47 +13335,47 @@
   order: desc</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="68" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="68" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>percent_of_total</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Share of all groups on this cut (source * 100 / partition sum).</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>share:
   op: percent_of_total
@@ -11239,47 +13383,47 @@
   partition_by: [region]</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>PercentOfTotal</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14" ht="81" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="81" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>ntile</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Bucket groups into N tiles using RANK-style ties.</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>value_quartile:
   op: ntile
@@ -11288,47 +13432,47 @@
   order: desc</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Ntile</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15" ht="68" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="68" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>dense_rank</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Rank groups on a cut. Ties share a rank; the next rank does not skip.</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>reason_dense_rank:
   op: dense_rank
@@ -11336,47 +13480,47 @@
   order: desc</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>DenseRank</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="68" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="68" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>row_number</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Unique 1..n order on a cut. Nulls sort last.</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>reason_row:
   op: row_number
@@ -11384,47 +13528,47 @@
   order: desc</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>RowNumber</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="68" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="68" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>cumulative_share</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Running share of of (Pareto). Last row in desc order is 100.</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>pareto:
   op: cumulative_share
@@ -11432,47 +13576,47 @@
   order: desc</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>CumulativeShare</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="68" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="68" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>running_total</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Ordered running sum of of on the cut.</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>running:
   op: running_total
@@ -11480,47 +13624,47 @@
   order: desc</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>RunningTotal</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="68" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="68" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>contribution</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Share of the cut's (of - vs) change. Who drove the movement.</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>yoy_contrib:
   op: contribution
@@ -11528,47 +13672,47 @@
   vs: previous_year_value</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>Contribution</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20" ht="68" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="68" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>lag</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Value of a base or shiftable measure over the selection shifted by offset.</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>value_3m_ly:
   op: lag
@@ -11576,47 +13720,47 @@
   offset: { years: 1 }</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr"/>
-      <c r="K20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="68" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="68" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>lead</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Value of a base or shiftable measure over the selection shifted forward by offset.</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>next_month:
   op: lead
@@ -11624,47 +13768,47 @@
   offset: { months: 1 }</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22" ht="68" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="68" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>of / lagged of × 100 over the selection vs the shifted selection. Source is a base or shiftable measure. 100 means unchanged.</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>volume_index:
   op: index
@@ -11672,47 +13816,47 @@
   offset: { years: 1 }</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="81" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>vs_target</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Compare of to a target measure or literal (gap or percent).</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>gap:
   op: vs_target
@@ -11721,47 +13865,47 @@
   as: gap</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>VsTarget</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="81" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>threshold</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>1 if of meets cmp vs a literal or measure, else 0.</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>hit_sla:
   op: threshold
@@ -11770,47 +13914,47 @@
   value: 95</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25" ht="68" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="68" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>percent_rank</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>RANK-style percent rank on a cut, scaled 0-100. One group is 0.</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>reason_pct_rank:
   op: percent_rank
@@ -11818,188 +13962,188 @@
   order: desc</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>PercentRank</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26" ht="55" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="55" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>gap_to_leader</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>of minus the partition max. The leader is 0.</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>vs_best:
   op: gap_to_leader
   of: current_value</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>GapToLeader</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27" ht="55" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="55" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>gap_to_avg</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>of minus the partition mean.</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>vs_typical:
   op: gap_to_avg
   of: current_value</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>GapToAvg</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28" ht="55" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="55" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>zscore</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>(of - mean) / sample stdev on the partition. Zero stdev is 0.</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>reason_z:
   op: zscore
   of: current_value</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>ZScore</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29" ht="68" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="68" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>running_avg</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Ordered running mean of of on the cut.</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>running_mean:
   op: running_avg
@@ -12007,47 +14151,47 @@
   order: desc</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>RunningAvg</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30" ht="81" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="81" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>top_n</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>1 if RANK() is &lt;= n, else 0. Ties can produce more than n ones.</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>top_reason:
   op: top_n
@@ -12056,47 +14200,47 @@
   order: desc</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.cut</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>TopN</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31" ht="68" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="68" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>diff</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>of minus the same measure over the selection shifted by offset. Source is a base or shiftable measure.</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>vs_last_year:
   op: diff
@@ -12104,47 +14248,47 @@
   offset: { years: 1 }</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32" ht="68" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="68" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>pct_change</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>addon</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>growth_pct(of, lagged of) over the selection vs the shifted selection. Source is a base or shiftable measure. Same scale as fn growth_pct.</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>yoy:
   op: pct_change
@@ -12152,23 +14296,1291 @@
   offset: { years: 1 }</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>kpi_engine.capabilities.ops.period</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>PctChange</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="5" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="68" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>compare</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Bind-time sugar; expands to pct_change or diff. Not evaluated. Period comparison presets (yoy, mom, wow, qoq, pop, diff, pct_change).</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>yoy:
+  op: compare
+  of: sotif_value
+  mode: yoy</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.period</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Compare</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="81" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>filtered_point</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Bind-time sugar; expands to point of a masked base. Not evaluated. Conditional sum/count at the selected period (column: or of: a base).</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>closed_amount:
+  op: filtered_point
+  column: amount
+  agg: sum
+  where: { column: status, op: eq, value: closed }</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>FilteredPoint</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="107" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>filtered_window</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Bind-time sugar; expands to window of a masked base. Not evaluated. Trailing or period-to-date aggregate of a filtered fact.</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>closed_3m:
+  op: filtered_window
+  column: amount
+  agg: sum
+  where: { column: status, op: eq, value: closed }
+  trailing: { months: 3 }
+  inclusive: true</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>FilteredWindow</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="120" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>filtered_trend</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Bind-time sugar; expands to trend of a masked base. Not evaluated. Sparkline of a filtered fact.</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>closed_trend_12m:
+  op: filtered_trend
+  column: amount
+  agg: sum
+  where: { column: status, op: eq, value: closed }
+  trailing: { months: 12 }
+  inclusive: true
+  cuts: [G]</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>FilteredTrend</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38" ht="94" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>filtered_compare</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Bind-time sugar; expands to compare then pct_change/diff of a masked base. Not evaluated. Filtered fact plus a compare preset in one measure key.</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>closed_yoy:
+  op: filtered_compare
+  column: amount
+  agg: sum
+  where: { column: status, op: eq, value: closed }
+  mode: yoy</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>FilteredCompare</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="55" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>expanding_window</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Aggregate from span start (or year start) through the anchor.</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>ytd_expanding:
+  op: expanding_window
+  of: sotif_value</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>ExpandingWindow</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="94" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>shifted_trend</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Trend series shifted by offset.</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>trend_ly:
+  op: shifted_trend
+  of: sotif_value
+  trailing: { months: 12 }
+  offset: { years: 1 }
+  cuts: [G]</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>ShiftedTrend</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="68" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>of / vs, or of / n.</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>per_period:
+  op: rate
+  of: sotif_value
+  n: 3</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42" ht="55" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>cumulative_point</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Period-to-date (cumulative) aggregate of a base at the anchor.</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>ytd:
+  op: cumulative_point
+  of: sotif_value</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>CumulativePoint</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43" ht="68" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>n_period_avg</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Mean of per-period values over trailing N.</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>avg_3m:
+  op: n_period_avg
+  of: sotif_value
+  trailing: { months: 3 }</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>NPeriodAvg</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44" ht="81" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>weighted_window</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Trailing window weighted by another base measure.</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>wavg_3m:
+  op: weighted_window
+  of: sotif_value
+  weight: sotif_value
+  trailing: { months: 3 }</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>WeightedWindow</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="81" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>snapshot_compare</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Compare two current scalars (pct or diff) without an offset.</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>vs_target:
+  op: snapshot_compare
+  of: current_value
+  vs: value_3m
+  mode: pct</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>SnapshotCompare</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46" ht="81" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>bottom_n</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>1 if the group is in the bottom n of of on the cut.</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>worst:
+  op: bottom_n
+  of: current_value
+  n: 1
+  cuts: [G]</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.cut</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>BottomN</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="81" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>rank_pct_change</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Rank groups by period percent change of of.</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>movers:
+  op: rank_pct_change
+  of: current_value
+  offset: { years: 1 }
+  cuts: [G]</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.cut</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>RankPctChange</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48" ht="68" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>concentration</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Herfindahl-Hirschman index of of shares on the cut.</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>hhi:
+  op: concentration
+  of: current_value
+  cuts: [G]</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.cut</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Concentration</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49" ht="68" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>abc_class</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>String A/B/C class from cumulative share (default 80/95).</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>cls:
+  op: abc_class
+  of: current_value
+  cuts: [G]</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.cut</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>AbcClass</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50" ht="81" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>pareto_flag</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>1 if the group is inside the leading cumulative-share band.</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>top80:
+  op: pareto_flag
+  of: current_value
+  share: 80
+  cuts: [G]</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.cut</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>ParetoFlag</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="81" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>normalize</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>of / max(of) or of / sum(of) on the cut.</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>scaled:
+  op: normalize
+  of: current_value
+  method: max
+  cuts: [G]</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.cut</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>Normalize</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52" ht="68" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>annualize</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Scale of to a year using periods_per_year / n.</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>annual:
+  op: annualize
+  of: current_value
+  n: 1</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.period</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Annualize</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="81" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>vs_prior_window</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Trailing window vs the same window shifted by offset.</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>win_yoy:
+  op: vs_prior_window
+  of: sotif_value
+  trailing: { months: 3 }
+  offset: { years: 1 }</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.period</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>VsPriorWindow</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54" ht="68" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>delta_contribution</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Current minus lagged of (or minus vs).</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>delta:
+  op: delta_contribution
+  of: current_value
+  offset: { years: 1 }</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.period</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>DeltaContribution</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55" ht="68" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>baseline_index</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>of / vs × 100. vs may be a measure or lagged of.</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>idx:
+  op: baseline_index
+  of: current_value
+  offset: { years: 1 }</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.period</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>BaselineIndex</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56" ht="94" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Factor or offset band around of. Bind expands to {key}_low and {key}_high unless emit: names a single side.</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>value_band:
+  op: band
+  of: current_value
+  method: factor
+  low: 0.8
+  high: 1.2</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57" ht="81" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>envelope</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Alias of band — dual keys {key}_low / {key}_high.</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>value_env:
+  op: envelope
+  of: current_value
+  low: 0.9
+  high: 1.1</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.combo</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>Envelope</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58" ht="68" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>compound_growth</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>(end/start)^(1/n) − 1 over a fixed N periods. Use hook:cagr for a trailing observed series (mutually exclusive shapes — pick one).</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>growth_12:
+  op: compound_growth
+  of: sotif_value
+  n: 12</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.period</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>CompoundGrowth</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr"/>
+      <c r="K58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59" ht="68" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>seasonal_adjust</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>addon</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Deseasonalize current × overall mean / same-month mean in the trailing window.</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>adj:
+  op: seasonal_adjust
+  of: sotif_value
+  trailing: { months: 36 }</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Put under measures: as op: &lt;name&gt;. Combo ops (point/window/fn/…) run per group; cut ops (rank/share/…) need the full cut; period ops (lag/index/…) need time:.</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>kpi_engine.capabilities.ops.period</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>SeasonalAdjust</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
